--- a/2026/ROSALES/ENERO/expensas rosales Enero.xlsx
+++ b/2026/ROSALES/ENERO/expensas rosales Enero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ROSALES\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ROSALES\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1A930E-0B9C-4A68-AE5B-394B7FEC709B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6043901-7A20-40AF-86F2-1211428A237F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
   <si>
     <t>TOTAL</t>
   </si>
@@ -306,9 +306,6 @@
   </si>
   <si>
     <t>PUNITORIOS 4%</t>
-  </si>
-  <si>
-    <t>Se abona hasta el</t>
   </si>
   <si>
     <t>Leandro</t>
@@ -369,9 +366,6 @@
     <t>ARBA:</t>
   </si>
   <si>
-    <t>Subidos en 0CT 2025</t>
-  </si>
-  <si>
     <t>PUNITORIOS MAL COBRADOS</t>
   </si>
   <si>
@@ -381,42 +375,31 @@
     <t>SIN EDESUR</t>
   </si>
   <si>
-    <t>TSG MES 11</t>
-  </si>
-  <si>
-    <t>SAC</t>
-  </si>
-  <si>
-    <t>Cerrajeria Aryam - Copia de llaves</t>
-  </si>
-  <si>
-    <t>PREVISION EXTRAORDINARIA - ARBA - ULTIMA CUOTA PERIODO 2025</t>
-  </si>
-  <si>
-    <t>CUOTA PLAN DE PAGOS (5/6)</t>
-  </si>
-  <si>
-    <t>RECUPERO DE DEUDORES DE EDESUR  HISTORICOS - LEER CARTEL VERDE</t>
-  </si>
-  <si>
-    <t>Vto. 16/01</t>
-  </si>
-  <si>
     <t>LIQUIDACIÓN EXPENSAS ENERO 2025</t>
   </si>
   <si>
-    <t>Estimados, buenos días / buenas tardes,
-A partir de las expensas emitidas desde ENERO de 2025, el consumo y pago de EDESUR deja de contabilizarse por separado y pasa a estar incluido dentro de los gastos ordinarios mensuales.
-De esta manera, el consorcio pasa a manejar una única caja, donde se reflejan todos los ingresos y egresos (EDESUR, seguros, AYSA, mantenimiento, sueldos, TSG, etc.), logrando mayor claridad y control.
-Desde ahora:
- • El monto correspondiente a EDESUR figurará en el prorrateo de cada unidad.
- • Estará incluido en el total a pagar.
- • El pago mensual de EDESUR se verá reflejado dentro de la caja general de expensas.
-Esta unificación evita desbalances y cruces de fondos que se daban anteriormente.
-Quedamos a disposición por cualquier consulta.</t>
-  </si>
-  <si>
     <t>EGRESOS DEL MES DE ENERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subidos en EN3R0 </t>
+  </si>
+  <si>
+    <t>TSG MES 12</t>
+  </si>
+  <si>
+    <t>Servisur - cambio de plafones en sala de medidores</t>
+  </si>
+  <si>
+    <t>Casa ruan - Compra de materiales electricos</t>
+  </si>
+  <si>
+    <t>Vto. 16/02</t>
+  </si>
+  <si>
+    <t>CUOTA PLAN DE PAGOS (6/6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREVISION EXTRAORDINARIA </t>
   </si>
 </sst>
 </file>
@@ -438,7 +421,7 @@
     <numFmt numFmtId="173" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="174" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,21 +641,26 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,12 +724,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF09FF09"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1049,7 +1031,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1174,7 +1156,6 @@
     <xf numFmtId="170" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1208,7 +1189,6 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1242,9 +1222,6 @@
     <xf numFmtId="0" fontId="27" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1278,8 +1255,6 @@
     <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="25" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1307,9 +1282,6 @@
     <xf numFmtId="171" fontId="25" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="25" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1346,8 +1318,6 @@
     <xf numFmtId="170" fontId="25" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="25" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="28" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="25" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1363,7 +1333,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1376,15 +1346,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1401,12 +1368,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1429,10 +1390,30 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="28" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="28" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="28" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1521,12 +1502,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>249555</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2274570" cy="914400"/>
+    <xdr:ext cx="2457450" cy="981076"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image1.jpg">
@@ -1546,8 +1527,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1259205" y="295276"/>
-          <a:ext cx="2274570" cy="914400"/>
+          <a:off x="6496050" y="409575"/>
+          <a:ext cx="2457450" cy="981076"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1850,17 +1831,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -1868,99 +1849,99 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="36"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="37"/>
       <c r="C17" s="33"/>
       <c r="D17" s="4"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="236">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="219">
-        <v>330057.21999999997</v>
+      <c r="C19" s="208">
+        <v>333245.92</v>
       </c>
       <c r="D19" s="20"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>25</v>
       </c>
@@ -1971,32 +1952,32 @@
       <c r="D20" s="20"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="236">
+      <c r="C21" s="33">
         <v>1034026.5</v>
       </c>
       <c r="D21" s="20"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="33">
-        <v>15748</v>
+        <v>21996</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6"/>
       <c r="F22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>11</v>
       </c>
@@ -2004,29 +1985,29 @@
         <v>22</v>
       </c>
       <c r="C23" s="33">
-        <v>83400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>89200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="40"/>
       <c r="B24" s="41"/>
       <c r="C24" s="23">
         <f>SUM(C17:C23)</f>
-        <v>1624885.72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+        <v>1640122.42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="39"/>
-      <c r="C25" s="220"/>
+      <c r="C25" s="209"/>
       <c r="D25" s="45"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="33">
@@ -2036,42 +2017,42 @@
       <c r="D26" s="45"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="42"/>
+        <v>97</v>
+      </c>
+      <c r="B27" s="28"/>
       <c r="C27" s="33">
-        <v>192033.53</v>
+        <v>5684</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B28" s="42"/>
       <c r="C28" s="33">
-        <v>5684</v>
+        <v>54000</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="33">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="D29" s="45"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="33">
@@ -2079,7 +2060,7 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>91</v>
       </c>
@@ -2089,74 +2070,74 @@
       <c r="E31" s="6"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="40"/>
       <c r="B32" s="41"/>
       <c r="C32" s="23">
         <f>SUM(C25:C31)</f>
-        <v>646784.58699999994</v>
+        <v>516751.05699999997</v>
       </c>
       <c r="F32" s="12"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="30"/>
       <c r="C33" s="43">
         <f>+C32+C24</f>
-        <v>2271670.307</v>
+        <v>2156873.477</v>
       </c>
       <c r="F33" s="12"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
-      <c r="C36" s="211"/>
+      <c r="C36" s="202"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="211"/>
+      <c r="C37" s="202"/>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
-    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C39" s="25"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="173" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" s="173"/>
-      <c r="C40" s="174">
-        <v>1000000</v>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="167" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="167"/>
+      <c r="C40" s="168">
+        <v>0</v>
       </c>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C41" s="25"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>15</v>
       </c>
@@ -2167,207 +2148,172 @@
       </c>
       <c r="E42" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>7</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="19">
         <f>+C42+C33</f>
-        <v>2271670.307</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B46" s="226"/>
-      <c r="C46" s="226"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="226"/>
-      <c r="B47" s="226"/>
-      <c r="C47" s="226"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="226"/>
-      <c r="B48" s="226"/>
-      <c r="C48" s="226"/>
-    </row>
-    <row r="49" spans="1:6" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="226"/>
-      <c r="B49" s="226"/>
-      <c r="C49" s="226"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="C50" s="154"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="200" t="s">
-        <v>100</v>
+        <v>2156873.477</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4"/>
+      <c r="C46" s="149"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="192" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="193">
+        <v>39116.323591710112</v>
+      </c>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="192" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="207">
+        <f>-(C44-C31)</f>
+        <v>-2156873.477</v>
+      </c>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="194">
+        <f>'prorrateo '!F31</f>
+        <v>2899814.6830321611</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="192" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="206">
+        <v>-1018468.24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="192" t="s">
+        <v>112</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="201">
-        <v>1137430.0615210002</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="200" t="s">
-        <v>126</v>
+      <c r="C51" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="192" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="28"/>
-      <c r="C52" s="218">
-        <f>-(C44-C31)</f>
-        <v>-2271670.307</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="200" t="s">
-        <v>96</v>
+      <c r="C52" s="231">
+        <v>107386.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="192" t="s">
+        <v>8</v>
       </c>
       <c r="B53" s="28"/>
-      <c r="C53" s="202">
-        <f>'prorrateo '!F31</f>
-        <v>2466028.3590707099</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="200" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="217">
-        <f>-Edesur!C7</f>
-        <v>-666521.55000000005</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="200" t="s">
-        <v>114</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="200" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="218">
-        <v>-1767562.94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="200" t="s">
-        <v>121</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="202">
-        <v>107386.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="200" t="s">
-        <v>8</v>
+      <c r="C53" s="193">
+        <f>SUM(C47:C52)</f>
+        <v>-129024.51037612879</v>
+      </c>
+      <c r="D53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="10"/>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="210"/>
+      <c r="B55" s="210"/>
+      <c r="C55" s="210"/>
+      <c r="F55" s="44"/>
+    </row>
+    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="211"/>
+      <c r="B56" s="211"/>
+      <c r="C56" s="211"/>
+    </row>
+    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="27"/>
+      <c r="C57" s="29"/>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="B58" s="28"/>
-      <c r="C58" s="201">
-        <f>SUM(C51:C57)</f>
-        <v>-994910.17640828993</v>
-      </c>
-      <c r="D58" s="5"/>
-    </row>
-    <row r="59" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="10"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="221"/>
-      <c r="B60" s="221"/>
-      <c r="C60" s="221"/>
-      <c r="F60" s="44"/>
-    </row>
-    <row r="61" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="222"/>
-      <c r="B61" s="222"/>
-      <c r="C61" s="222"/>
-    </row>
-    <row r="62" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B62" s="27"/>
-      <c r="C62" s="29"/>
-    </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="31">
+      <c r="C58" s="31">
         <f>-C42</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="31"/>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="32"/>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="155" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="156"/>
-      <c r="C66" s="157">
-        <f>SUM(C62:C65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="223" t="s">
-        <v>108</v>
-      </c>
-      <c r="B67" s="224"/>
-      <c r="C67" s="224"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="224"/>
-      <c r="B68" s="224"/>
-      <c r="C68" s="224"/>
-    </row>
-    <row r="69" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="224"/>
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="31"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="32"/>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="151"/>
+      <c r="C61" s="152">
+        <f>SUM(C57:C60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="212" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" s="213"/>
+      <c r="C62" s="213"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="213"/>
+      <c r="B63" s="213"/>
+      <c r="C63" s="213"/>
+    </row>
+    <row r="64" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="213"/>
+      <c r="B64" s="213"/>
+      <c r="C64" s="213"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A60:C61"/>
-    <mergeCell ref="A67:C69"/>
-    <mergeCell ref="A46:C49"/>
+  <mergeCells count="2">
+    <mergeCell ref="A55:C56"/>
+    <mergeCell ref="A62:C64"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2386,63 +2332,63 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" customWidth="1"/>
-    <col min="9" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
+    <col min="9" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="11" customWidth="1"/>
     <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="227">
+        <v>102</v>
+      </c>
+      <c r="B1" s="214">
         <f>N1</f>
-        <v>1237643.807</v>
-      </c>
-      <c r="C1" s="227"/>
-      <c r="D1" s="138">
+        <v>2156873.477</v>
+      </c>
+      <c r="C1" s="214"/>
+      <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="230" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="227">
-        <v>1000000</v>
-      </c>
-      <c r="M1" s="227"/>
+        <v>101</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="217" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="214">
+        <v>0</v>
+      </c>
+      <c r="M1" s="214"/>
       <c r="N1">
-        <v>1237643.807</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2156873.477</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="134" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="47" t="s">
@@ -2457,29 +2403,29 @@
       <c r="G2" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="199" t="s">
+      <c r="H2" s="191" t="s">
         <v>92</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L2" s="50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M2" s="51" t="s">
         <v>30</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>31</v>
       </c>
@@ -2492,14 +2438,14 @@
       <c r="D3" s="55">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E3" s="129">
-        <v>134104.34113548099</v>
-      </c>
-      <c r="F3" s="214">
+      <c r="E3" s="126">
+        <v>153001.36328172</v>
+      </c>
+      <c r="F3" s="225">
         <f>E3</f>
-        <v>134104.34113548099</v>
-      </c>
-      <c r="G3" s="56">
+        <v>153001.36328172</v>
+      </c>
+      <c r="G3" s="226">
         <f>E3-F3</f>
         <v>0</v>
       </c>
@@ -2509,11 +2455,11 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>63243.598537700011</v>
+        <v>110216.2346747</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
-        <v>38657.764744019987</v>
+        <v>57666.630048390034</v>
       </c>
       <c r="K3" s="56">
         <f>G$1*D3/100</f>
@@ -2521,24 +2467,24 @@
       </c>
       <c r="L3" s="56">
         <f>L$1*D3/100</f>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>153001.36328172</v>
+        <v>167882.86472309002</v>
       </c>
       <c r="N3" s="44"/>
-      <c r="O3" s="151">
+      <c r="O3" s="146">
         <f>M3-J3</f>
-        <v>114343.59853770002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110216.23467469998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="58" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="60" t="s">
         <v>34</v>
@@ -2546,14 +2492,14 @@
       <c r="D4" s="61">
         <v>5.09</v>
       </c>
-      <c r="E4" s="129">
-        <v>130106.86867093903</v>
-      </c>
-      <c r="F4" s="214">
+      <c r="E4" s="126">
+        <v>148167.69116867997</v>
+      </c>
+      <c r="F4" s="225">
         <f>E4</f>
-        <v>130106.86867093903</v>
-      </c>
-      <c r="G4" s="56">
+        <v>148167.69116867997</v>
+      </c>
+      <c r="G4" s="226">
         <f t="shared" ref="G4:G29" si="0">E4-F4</f>
         <v>0</v>
       </c>
@@ -2563,11 +2509,11 @@
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="2">B$1*D4/100</f>
-        <v>62996.069776299999</v>
+        <v>109784.8599793</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
-        <v>34271.621392379988</v>
+        <v>50981.078611410012</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" ref="K4:K29" si="3">G$1*D4/100</f>
@@ -2575,19 +2521,19 @@
       </c>
       <c r="L4" s="56">
         <f t="shared" ref="L4:L29" si="4">L$1*D4/100</f>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
-        <v>148167.69116867997</v>
+        <v>160765.93859071002</v>
       </c>
       <c r="N4" s="44"/>
-      <c r="O4" s="151">
+      <c r="O4" s="146">
         <f t="shared" ref="O4:O29" si="6">M4-J4</f>
-        <v>113896.06977629999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>109784.8599793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
         <v>35</v>
       </c>
@@ -2598,28 +2544,28 @@
       <c r="D5" s="61">
         <v>5.04</v>
       </c>
-      <c r="E5" s="129">
-        <v>160726.72885904807</v>
-      </c>
-      <c r="F5" s="214">
-        <f>160000-F23</f>
-        <v>134409.67677473198</v>
-      </c>
-      <c r="G5" s="56">
+      <c r="E5" s="126">
+        <v>187753.45675376873</v>
+      </c>
+      <c r="F5" s="225">
+        <f>215804.85-F23</f>
+        <v>187753.46389584002</v>
+      </c>
+      <c r="G5" s="226">
         <f t="shared" si="0"/>
-        <v>26317.052084316092</v>
+        <v>-7.1420712920371443E-3</v>
       </c>
       <c r="H5" s="56">
         <f t="shared" si="1"/>
-        <v>1052.6820833726438</v>
+        <v>0</v>
       </c>
       <c r="I5" s="56">
         <f t="shared" si="2"/>
-        <v>62377.247872799999</v>
+        <v>108706.4232408</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
-        <v>47606.474713279997</v>
+        <v>69887.502618960018</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="3"/>
@@ -2627,51 +2573,48 @@
       </c>
       <c r="L5" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="M5" s="57">
         <f t="shared" si="5"/>
-        <v>187753.45675376873</v>
+        <v>178593.91871768871</v>
       </c>
       <c r="N5" s="44"/>
-      <c r="O5" s="151">
+      <c r="O5" s="146">
         <f t="shared" si="6"/>
-        <v>140146.98204048874</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>108706.41609872869</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="198"/>
+      <c r="B6" s="190"/>
       <c r="C6" s="63" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="176">
+      <c r="D6" s="170">
         <v>5.21</v>
       </c>
-      <c r="E6" s="129">
-        <v>242855.68957555902</v>
-      </c>
-      <c r="F6" s="214">
-        <f>E6</f>
-        <v>242855.68957555902</v>
-      </c>
-      <c r="G6" s="64">
+      <c r="E6" s="126">
+        <v>151256.37574692001</v>
+      </c>
+      <c r="F6" s="204"/>
+      <c r="G6" s="227">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>151256.37574692001</v>
       </c>
       <c r="H6" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6050.2550298768001</v>
       </c>
       <c r="I6" s="64">
         <f t="shared" si="2"/>
-        <v>64481.242344700004</v>
+        <v>112373.1081517</v>
       </c>
       <c r="J6" s="64">
         <f>Edesur!N13</f>
-        <v>34675.13340222001</v>
+        <v>41753.046533289991</v>
       </c>
       <c r="K6" s="64">
         <f t="shared" si="3"/>
@@ -2679,24 +2622,24 @@
       </c>
       <c r="L6" s="64">
         <f t="shared" si="4"/>
-        <v>52100</v>
-      </c>
-      <c r="M6" s="213">
+        <v>0</v>
+      </c>
+      <c r="M6" s="203">
         <f t="shared" si="5"/>
-        <v>151256.37574692001</v>
-      </c>
-      <c r="O6" s="151">
+        <v>311432.78546178679</v>
+      </c>
+      <c r="O6" s="146">
         <f t="shared" si="6"/>
-        <v>116581.2423447</v>
-      </c>
-      <c r="P6" s="175"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>269679.73892849678</v>
+      </c>
+      <c r="P6" s="169"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="60" t="s">
         <v>39</v>
@@ -2704,16 +2647,16 @@
       <c r="D7" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E7" s="129">
-        <v>130486.97654548101</v>
-      </c>
-      <c r="F7" s="214">
-        <f t="shared" ref="F7:F11" si="7">E7</f>
-        <v>130486.97654548101</v>
-      </c>
-      <c r="G7" s="56">
+      <c r="E7" s="126">
+        <v>152954.46978172002</v>
+      </c>
+      <c r="F7" s="225">
+        <f>181005.86-F28</f>
+        <v>152954.47389584</v>
+      </c>
+      <c r="G7" s="226">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-4.1141199762932956E-3</v>
       </c>
       <c r="H7" s="56">
         <f t="shared" si="1"/>
@@ -2721,11 +2664,11 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="2"/>
-        <v>63243.598537700011</v>
+        <v>110216.2346747</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
-        <v>38610.871244020003</v>
+        <v>57479.05604838999</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" si="3"/>
@@ -2733,19 +2676,19 @@
       </c>
       <c r="L7" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="M7" s="57">
         <f t="shared" si="5"/>
-        <v>152954.46978172002</v>
-      </c>
-      <c r="O7" s="151">
+        <v>167695.28660897003</v>
+      </c>
+      <c r="O7" s="146">
         <f t="shared" si="6"/>
-        <v>114343.59853770002</v>
-      </c>
-      <c r="P7" s="175"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110216.23056058004</v>
+      </c>
+      <c r="P7" s="169"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
         <v>40</v>
       </c>
@@ -2756,14 +2699,14 @@
       <c r="D8" s="61">
         <v>5.09</v>
       </c>
-      <c r="E8" s="129">
-        <v>128193.61387093902</v>
-      </c>
-      <c r="F8" s="214">
-        <f t="shared" si="7"/>
-        <v>128193.61387093902</v>
-      </c>
-      <c r="G8" s="56">
+      <c r="E8" s="126">
+        <v>153579.20106868001</v>
+      </c>
+      <c r="F8" s="225">
+        <f t="shared" ref="F7:F11" si="7">E8</f>
+        <v>153579.20106868001</v>
+      </c>
+      <c r="G8" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2773,11 +2716,11 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="2"/>
-        <v>62996.069776299999</v>
+        <v>109784.8599793</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
-        <v>39683.131292380014</v>
+        <v>57705.606511409991</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" si="3"/>
@@ -2785,18 +2728,18 @@
       </c>
       <c r="L8" s="56">
         <f t="shared" si="4"/>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="M8" s="57">
         <f t="shared" si="5"/>
-        <v>153579.20106868001</v>
-      </c>
-      <c r="O8" s="151">
+        <v>167490.46649070998</v>
+      </c>
+      <c r="O8" s="146">
         <f t="shared" si="6"/>
-        <v>113896.06977629999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>109784.85997929999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
         <v>42</v>
       </c>
@@ -2807,16 +2750,16 @@
       <c r="D9" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E9" s="129">
-        <v>129633.514845481</v>
-      </c>
-      <c r="F9" s="214">
-        <f>130000</f>
-        <v>130000</v>
-      </c>
-      <c r="G9" s="56">
+      <c r="E9" s="126">
+        <v>145197.56902720104</v>
+      </c>
+      <c r="F9" s="225">
+        <f>E9</f>
+        <v>145197.56902720104</v>
+      </c>
+      <c r="G9" s="226">
         <f t="shared" si="0"/>
-        <v>-366.48515451900312</v>
+        <v>0</v>
       </c>
       <c r="H9" s="56">
         <f t="shared" si="1"/>
@@ -2824,11 +2767,11 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="2"/>
-        <v>63243.598537700011</v>
+        <v>110216.2346747</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
-        <v>31220.45564402001</v>
+        <v>44217.574248389981</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" si="3"/>
@@ -2836,71 +2779,71 @@
       </c>
       <c r="L9" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="57">
         <f t="shared" si="5"/>
-        <v>145197.56902720104</v>
-      </c>
-      <c r="O9" s="151">
+        <v>154433.80892308999</v>
+      </c>
+      <c r="O9" s="146">
         <f t="shared" si="6"/>
-        <v>113977.11338318103</v>
-      </c>
-      <c r="P9" s="175"/>
-    </row>
-    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="177" t="s">
+        <v>110216.23467470001</v>
+      </c>
+      <c r="P9" s="169"/>
+    </row>
+    <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="178" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="179" t="s">
+      <c r="B10" s="172" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="180">
+      <c r="D10" s="174">
         <v>5.09</v>
       </c>
-      <c r="E10" s="181">
-        <v>122885.26967093899</v>
-      </c>
-      <c r="F10" s="215">
+      <c r="E10" s="175">
+        <v>135028.13246867998</v>
+      </c>
+      <c r="F10" s="230">
         <f t="shared" si="7"/>
-        <v>122885.26967093899</v>
-      </c>
-      <c r="G10" s="182">
+        <v>135028.13246867998</v>
+      </c>
+      <c r="G10" s="228">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="182"/>
-      <c r="I10" s="182">
+      <c r="H10" s="176"/>
+      <c r="I10" s="176">
         <f t="shared" si="2"/>
-        <v>62996.069776299999</v>
-      </c>
-      <c r="J10" s="182">
+        <v>109784.8599793</v>
+      </c>
+      <c r="J10" s="176">
         <f>Edesur!N17</f>
-        <v>21132.062692379994</v>
-      </c>
-      <c r="K10" s="182">
+        <v>38179.153111410007</v>
+      </c>
+      <c r="K10" s="176">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="182">
+      <c r="L10" s="176">
         <f t="shared" si="4"/>
-        <v>50900</v>
-      </c>
-      <c r="M10" s="183">
+        <v>0</v>
+      </c>
+      <c r="M10" s="177">
         <f t="shared" si="5"/>
-        <v>135028.13246867998</v>
-      </c>
-      <c r="O10" s="151">
+        <v>147964.01309071001</v>
+      </c>
+      <c r="O10" s="146">
         <f t="shared" si="6"/>
-        <v>113896.06977629999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>109784.8599793</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="59"/>
       <c r="C11" s="60" t="s">
@@ -2909,28 +2852,25 @@
       <c r="D11" s="61">
         <v>5.04</v>
       </c>
-      <c r="E11" s="129">
-        <v>127318.37378458401</v>
-      </c>
-      <c r="F11" s="214">
-        <f t="shared" si="7"/>
-        <v>127318.37378458401</v>
-      </c>
-      <c r="G11" s="56">
+      <c r="E11" s="126">
+        <v>143136.29328608001</v>
+      </c>
+      <c r="F11" s="204"/>
+      <c r="G11" s="226">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>143136.29328608001</v>
       </c>
       <c r="H11" s="56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5725.4517314432005</v>
       </c>
       <c r="I11" s="56">
         <f t="shared" si="2"/>
-        <v>62377.247872799999</v>
+        <v>108706.4232408</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
-        <v>30359.045413280011</v>
+        <v>46037.468518960013</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" si="3"/>
@@ -2938,18 +2878,18 @@
       </c>
       <c r="L11" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="M11" s="57">
         <f t="shared" si="5"/>
-        <v>143136.29328608001</v>
-      </c>
-      <c r="O11" s="151">
+        <v>303605.63677728322</v>
+      </c>
+      <c r="O11" s="146">
         <f t="shared" si="6"/>
-        <v>112777.2478728</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>257568.16825832322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="58" t="s">
         <v>47</v>
       </c>
@@ -2960,14 +2900,14 @@
       <c r="D12" s="61">
         <v>5.21</v>
       </c>
-      <c r="E12" s="129">
-        <v>144392.25191819097</v>
-      </c>
-      <c r="F12" s="214">
+      <c r="E12" s="126">
+        <v>167106.37874692006</v>
+      </c>
+      <c r="F12" s="225">
         <f t="shared" ref="F12" si="8">E12</f>
-        <v>144392.25191819097</v>
-      </c>
-      <c r="G12" s="56">
+        <v>167106.37874692006</v>
+      </c>
+      <c r="G12" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2977,11 +2917,11 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="2"/>
-        <v>64481.242344700004</v>
+        <v>112373.1081517</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
-        <v>50525.136402220058</v>
+        <v>62264.263433289976</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="3"/>
@@ -2989,18 +2929,18 @@
       </c>
       <c r="L12" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="M12" s="57">
         <f t="shared" si="5"/>
-        <v>167106.37874692006</v>
-      </c>
-      <c r="O12" s="151">
+        <v>174637.37158498997</v>
+      </c>
+      <c r="O12" s="146">
         <f t="shared" si="6"/>
-        <v>116581.2423447</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>112373.1081517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
         <v>49</v>
       </c>
@@ -3013,16 +2953,16 @@
       <c r="D13" s="61">
         <v>5.1100000000000003</v>
       </c>
-      <c r="E13" s="129">
-        <v>175045.18024548097</v>
-      </c>
-      <c r="F13" s="214">
-        <f>E13</f>
-        <v>175045.18024548097</v>
-      </c>
-      <c r="G13" s="56">
+      <c r="E13" s="126">
+        <v>162201.86798172005</v>
+      </c>
+      <c r="F13" s="225">
+        <f>190253.26-F24</f>
+        <v>162201.87389584002</v>
+      </c>
+      <c r="G13" s="226">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5.9141199744772166E-3</v>
       </c>
       <c r="H13" s="56">
         <f t="shared" si="1"/>
@@ -3030,11 +2970,11 @@
       </c>
       <c r="I13" s="56">
         <f t="shared" si="2"/>
-        <v>63243.598537700011</v>
+        <v>110216.2346747</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
-        <v>47858.269444020021</v>
+        <v>66144.974848390004</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" si="3"/>
@@ -3042,53 +2982,53 @@
       </c>
       <c r="L13" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="M13" s="57">
         <f t="shared" si="5"/>
-        <v>162201.86798172005</v>
+        <v>176361.20360897004</v>
       </c>
       <c r="N13" s="44"/>
-      <c r="O13" s="151">
+      <c r="O13" s="146">
         <f t="shared" si="6"/>
-        <v>114343.59853770002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110216.22876058004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="198" t="s">
-        <v>106</v>
+      <c r="B14" s="190" t="s">
+        <v>105</v>
       </c>
       <c r="C14" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="176">
+      <c r="D14" s="170">
         <v>5.09</v>
       </c>
-      <c r="E14" s="129">
-        <v>83972.551670038971</v>
-      </c>
-      <c r="F14" s="214">
-        <f>109600-F25</f>
-        <v>84009.676774731997</v>
-      </c>
-      <c r="G14" s="64">
+      <c r="E14" s="126">
+        <v>138995.71226398699</v>
+      </c>
+      <c r="F14" s="225">
+        <f>167047.02-F25</f>
+        <v>138995.63389584</v>
+      </c>
+      <c r="G14" s="227">
         <f t="shared" si="0"/>
-        <v>-37.125104693026515</v>
+        <v>7.8368146991124377E-2</v>
       </c>
       <c r="H14" s="64">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.134725879644975E-3</v>
       </c>
       <c r="I14" s="64">
         <f t="shared" si="2"/>
-        <v>62996.069776299999</v>
+        <v>109784.8599793</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
-        <v>25136.76759238002</v>
+        <v>41668.029511409994</v>
       </c>
       <c r="K14" s="64">
         <f t="shared" si="3"/>
@@ -3096,18 +3036,18 @@
       </c>
       <c r="L14" s="56">
         <f t="shared" si="4"/>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="M14" s="57">
         <f t="shared" si="5"/>
-        <v>138995.71226398699</v>
-      </c>
-      <c r="O14" s="151">
+        <v>151452.97099358286</v>
+      </c>
+      <c r="O14" s="146">
         <f t="shared" si="6"/>
-        <v>113858.94467160697</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>109784.94148217287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>53</v>
       </c>
@@ -3120,25 +3060,28 @@
       <c r="D15" s="61">
         <v>5.04</v>
       </c>
-      <c r="E15" s="129">
-        <v>124636.07021507998</v>
-      </c>
-      <c r="F15" s="214"/>
-      <c r="G15" s="56">
+      <c r="E15" s="126">
+        <v>279407.3046097632</v>
+      </c>
+      <c r="F15" s="225">
+        <f>334072.62-F29</f>
+        <v>279407.29774156125</v>
+      </c>
+      <c r="G15" s="226">
         <f t="shared" si="0"/>
-        <v>124636.07021507998</v>
+        <v>6.8682019482366741E-3</v>
       </c>
       <c r="H15" s="56">
         <f t="shared" si="1"/>
-        <v>4985.4428086031994</v>
+        <v>2.7472807792946699E-4</v>
       </c>
       <c r="I15" s="56">
         <f t="shared" si="2"/>
-        <v>62377.247872799999</v>
+        <v>108706.4232408</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
-        <v>37008.543713280022</v>
+        <v>44386.817318959977</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" si="3"/>
@@ -3146,18 +3089,18 @@
       </c>
       <c r="L15" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="M15" s="57">
         <f t="shared" si="5"/>
-        <v>279407.3046097632</v>
-      </c>
-      <c r="O15" s="151">
+        <v>153093.24770269002</v>
+      </c>
+      <c r="O15" s="146">
         <f t="shared" si="6"/>
-        <v>242398.76089648317</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>108706.43038373004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="58" t="s">
         <v>56</v>
       </c>
@@ -3170,16 +3113,16 @@
       <c r="D16" s="61">
         <v>5.21</v>
       </c>
-      <c r="E16" s="129">
-        <v>134085.060618191</v>
-      </c>
-      <c r="F16" s="214">
-        <f t="shared" ref="F16:F21" si="9">E16</f>
-        <v>134085.060618191</v>
-      </c>
-      <c r="G16" s="56">
+      <c r="E16" s="126">
+        <v>159322.05774691998</v>
+      </c>
+      <c r="F16" s="225">
+        <f>187373.45-F21</f>
+        <v>159322.06389584002</v>
+      </c>
+      <c r="G16" s="226">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6.1489200452342629E-3</v>
       </c>
       <c r="H16" s="56">
         <f t="shared" si="1"/>
@@ -3187,11 +3130,11 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="2"/>
-        <v>64481.242344700004</v>
+        <v>112373.1081517</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
-        <v>42740.815402219974</v>
+        <v>66334.619233290025</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" si="3"/>
@@ -3199,19 +3142,19 @@
       </c>
       <c r="L16" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="M16" s="57">
         <f t="shared" si="5"/>
-        <v>159322.05774691998</v>
+        <v>178707.72123606998</v>
       </c>
       <c r="N16" s="44"/>
-      <c r="O16" s="151">
+      <c r="O16" s="146">
         <f t="shared" si="6"/>
-        <v>116581.2423447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>112373.10200277995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="58" t="s">
         <v>59</v>
       </c>
@@ -3222,16 +3165,16 @@
       <c r="D17" s="61">
         <v>5.04</v>
       </c>
-      <c r="E17" s="129">
-        <v>121859.97038458401</v>
-      </c>
-      <c r="F17" s="214">
-        <f t="shared" si="9"/>
-        <v>121859.97038458401</v>
-      </c>
-      <c r="G17" s="56">
+      <c r="E17" s="126">
+        <v>135108.12608607998</v>
+      </c>
+      <c r="F17" s="225">
+        <f>E17+134891.87</f>
+        <v>269999.99608607998</v>
+      </c>
+      <c r="G17" s="226">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-134891.87</v>
       </c>
       <c r="H17" s="56">
         <f t="shared" si="1"/>
@@ -3239,11 +3182,11 @@
       </c>
       <c r="I17" s="56">
         <f t="shared" si="2"/>
-        <v>62377.247872799999</v>
+        <v>108706.4232408</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
-        <v>22330.878213279997</v>
+        <v>47781.906718960003</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" si="3"/>
@@ -3251,36 +3194,36 @@
       </c>
       <c r="L17" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="M17" s="57">
         <f t="shared" si="5"/>
-        <v>135108.12608607998</v>
-      </c>
-      <c r="O17" s="151">
+        <v>21596.459959760003</v>
+      </c>
+      <c r="O17" s="146">
         <f t="shared" si="6"/>
-        <v>112777.24787279998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="204" t="s">
+        <v>-26185.4467592</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="196" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="205"/>
+      <c r="B18" s="197"/>
       <c r="C18" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="176">
+      <c r="D18" s="170">
         <v>5.21</v>
       </c>
-      <c r="E18" s="129">
-        <v>130961.95351819103</v>
-      </c>
-      <c r="F18" s="214">
-        <f t="shared" si="9"/>
-        <v>130961.95351819103</v>
-      </c>
-      <c r="G18" s="64">
+      <c r="E18" s="126">
+        <v>142824.92444691999</v>
+      </c>
+      <c r="F18" s="225">
+        <f t="shared" ref="F16:F21" si="9">E18</f>
+        <v>142824.92444691999</v>
+      </c>
+      <c r="G18" s="227">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3290,11 +3233,11 @@
       </c>
       <c r="I18" s="64">
         <f t="shared" si="2"/>
-        <v>64481.242344700004</v>
+        <v>112373.1081517</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
-        <v>26243.682102220002</v>
+        <v>48121.183833290001</v>
       </c>
       <c r="K18" s="64">
         <f t="shared" si="3"/>
@@ -3302,39 +3245,39 @@
       </c>
       <c r="L18" s="64">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="57">
         <f t="shared" si="5"/>
-        <v>142824.92444691999</v>
-      </c>
-      <c r="N18" s="207"/>
-      <c r="O18" s="151">
+        <v>160494.29198499001</v>
+      </c>
+      <c r="N18" s="199"/>
+      <c r="O18" s="146">
         <f t="shared" si="6"/>
-        <v>116581.24234469999</v>
-      </c>
-      <c r="P18" s="206"/>
-      <c r="Q18" s="203"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>112373.1081517</v>
+      </c>
+      <c r="P18" s="198"/>
+      <c r="Q18" s="195"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="198"/>
+      <c r="B19" s="190"/>
       <c r="C19" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="176">
+      <c r="D19" s="170">
         <v>7.4</v>
       </c>
-      <c r="E19" s="129">
-        <v>190590.86978054006</v>
-      </c>
-      <c r="F19" s="214">
+      <c r="E19" s="126">
+        <v>225198.20842479993</v>
+      </c>
+      <c r="F19" s="225">
         <f t="shared" si="9"/>
-        <v>190590.86978054006</v>
-      </c>
-      <c r="G19" s="64">
+        <v>225198.20842479993</v>
+      </c>
+      <c r="G19" s="227">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3344,11 +3287,11 @@
       </c>
       <c r="I19" s="64">
         <f t="shared" si="2"/>
-        <v>91585.641717999999</v>
+        <v>159608.63729800002</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
-        <v>59612.566706799938</v>
+        <v>102681.15688260003</v>
       </c>
       <c r="K19" s="64">
         <f t="shared" si="3"/>
@@ -3356,66 +3299,66 @@
       </c>
       <c r="L19" s="64">
         <f t="shared" si="4"/>
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="M19" s="57">
         <f t="shared" si="5"/>
-        <v>225198.20842479993</v>
-      </c>
-      <c r="O19" s="151">
+        <v>262289.79418060003</v>
+      </c>
+      <c r="O19" s="146">
         <f t="shared" si="6"/>
-        <v>165585.641718</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="184"/>
-      <c r="B20" s="178" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="179" t="s">
+        <v>159608.63729799999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="178"/>
+      <c r="B20" s="172" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="180">
+      <c r="D20" s="174">
         <v>1.08</v>
       </c>
-      <c r="E20" s="181">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F20" s="215">
+      <c r="E20" s="175">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F20" s="230">
         <f t="shared" si="9"/>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G20" s="182">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G20" s="228">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="182"/>
-      <c r="I20" s="182">
+      <c r="H20" s="176"/>
+      <c r="I20" s="176">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
-      </c>
-      <c r="J20" s="182">
+        <v>23294.233551600002</v>
+      </c>
+      <c r="J20" s="176">
         <f>Edesur!N27</f>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="K20" s="182">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="K20" s="176">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20" s="182">
+      <c r="L20" s="176">
         <f t="shared" si="4"/>
-        <v>10800</v>
-      </c>
-      <c r="M20" s="183">
+        <v>0</v>
+      </c>
+      <c r="M20" s="177">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O20" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O20" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="62"/>
       <c r="B21" s="59" t="s">
         <v>57</v>
@@ -3426,14 +3369,14 @@
       <c r="D21" s="61">
         <v>1.08</v>
       </c>
-      <c r="E21" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F21" s="214">
+      <c r="E21" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F21" s="225">
         <f t="shared" si="9"/>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G21" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G21" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3443,11 +3386,11 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="3"/>
@@ -3455,66 +3398,66 @@
       </c>
       <c r="L21" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M21" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O21" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O21" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="139"/>
-      <c r="B22" s="140"/>
-      <c r="C22" s="141" t="s">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="136"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="142">
+      <c r="D22" s="139">
         <v>1.08</v>
       </c>
-      <c r="E22" s="143">
-        <v>298692.77884232404</v>
-      </c>
-      <c r="F22" s="216">
-        <v>0</v>
-      </c>
-      <c r="G22" s="144">
+      <c r="E22" s="140">
+        <v>338691.87610017706</v>
+      </c>
+      <c r="F22" s="205">
+        <v>0</v>
+      </c>
+      <c r="G22" s="229">
         <f t="shared" si="0"/>
-        <v>298692.77884232404</v>
-      </c>
-      <c r="H22" s="144">
+        <v>338691.87610017706</v>
+      </c>
+      <c r="H22" s="141">
         <f t="shared" si="1"/>
-        <v>11947.711153692962</v>
-      </c>
-      <c r="I22" s="144">
+        <v>13547.675044007083</v>
+      </c>
+      <c r="I22" s="141">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
-      </c>
-      <c r="J22" s="144">
+        <v>23294.233551600002</v>
+      </c>
+      <c r="J22" s="141">
         <f>Edesur!N29</f>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="K22" s="144">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="K22" s="141">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L22" s="144">
+      <c r="L22" s="141">
         <f t="shared" si="4"/>
-        <v>10800</v>
-      </c>
-      <c r="M22" s="145">
+        <v>0</v>
+      </c>
+      <c r="M22" s="142">
         <f t="shared" si="5"/>
-        <v>338691.87610017706</v>
-      </c>
-      <c r="O22" s="151">
+        <v>383051.60189270414</v>
+      </c>
+      <c r="O22" s="146">
         <f t="shared" si="6"/>
-        <v>334807.04311161704</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+        <v>375533.78469578415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="58" t="s">
         <v>35</v>
       </c>
@@ -3525,14 +3468,14 @@
       <c r="D23" s="61">
         <v>1.08</v>
       </c>
-      <c r="E23" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F23" s="214">
+      <c r="E23" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F23" s="225">
         <f>E23</f>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G23" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G23" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3542,11 +3485,11 @@
       </c>
       <c r="I23" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" si="3"/>
@@ -3554,18 +3497,18 @@
       </c>
       <c r="L23" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M23" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O23" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O23" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
         <v>49</v>
       </c>
@@ -3578,14 +3521,14 @@
       <c r="D24" s="61">
         <v>1.08</v>
       </c>
-      <c r="E24" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F24" s="214">
+      <c r="E24" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F24" s="225">
         <f t="shared" ref="F24" si="10">E24</f>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G24" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G24" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3595,11 +3538,11 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" si="3"/>
@@ -3607,23 +3550,23 @@
       </c>
       <c r="L24" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M24" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O24" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O24" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="198" t="s">
-        <v>106</v>
+      <c r="B25" s="190" t="s">
+        <v>105</v>
       </c>
       <c r="C25" s="60" t="s">
         <v>70</v>
@@ -3631,14 +3574,14 @@
       <c r="D25" s="61">
         <v>1.08</v>
       </c>
-      <c r="E25" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F25" s="214">
+      <c r="E25" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F25" s="225">
         <f>E25</f>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G25" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G25" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3648,11 +3591,11 @@
       </c>
       <c r="I25" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" si="3"/>
@@ -3660,18 +3603,18 @@
       </c>
       <c r="L25" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M25" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O25" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O25" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
         <v>63</v>
       </c>
@@ -3682,14 +3625,14 @@
       <c r="D26" s="61">
         <v>1.08</v>
       </c>
-      <c r="E26" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F26" s="214">
+      <c r="E26" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F26" s="225">
         <f t="shared" ref="F26:F28" si="11">E26</f>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G26" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G26" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3699,11 +3642,11 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" si="3"/>
@@ -3711,18 +3654,18 @@
       </c>
       <c r="L26" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M26" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O26" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O26" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
         <v>63</v>
       </c>
@@ -3733,14 +3676,14 @@
       <c r="D27" s="61">
         <v>1.08</v>
       </c>
-      <c r="E27" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F27" s="214">
+      <c r="E27" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F27" s="225">
         <f t="shared" si="11"/>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G27" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G27" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3750,11 +3693,11 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" si="3"/>
@@ -3762,22 +3705,22 @@
       </c>
       <c r="L27" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M27" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O27" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O27" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
-        <v>241771.51623107606</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>281300.98063311994</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="66"/>
       <c r="B28" s="65" t="str">
         <f>B7</f>
@@ -3789,14 +3732,14 @@
       <c r="D28" s="61">
         <v>1.08</v>
       </c>
-      <c r="E28" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F28" s="214">
+      <c r="E28" s="126">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="F28" s="225">
         <f t="shared" si="11"/>
-        <v>25590.323225268006</v>
-      </c>
-      <c r="G28" s="56">
+        <v>28051.386104159999</v>
+      </c>
+      <c r="G28" s="226">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3806,11 +3749,11 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" si="3"/>
@@ -3818,18 +3761,18 @@
       </c>
       <c r="L28" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M28" s="57">
         <f t="shared" si="5"/>
-        <v>28051.386104159999</v>
-      </c>
-      <c r="O28" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O28" s="146">
         <f t="shared" si="6"/>
-        <v>24166.5531156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="66" t="s">
         <v>53</v>
       </c>
@@ -3842,25 +3785,28 @@
       <c r="D29" s="61">
         <v>1.08</v>
       </c>
-      <c r="E29" s="129">
-        <v>25590.323225268006</v>
-      </c>
-      <c r="F29" s="210"/>
-      <c r="G29" s="56">
+      <c r="E29" s="126">
+        <v>54665.322258438733</v>
+      </c>
+      <c r="F29" s="225">
+        <f>E29</f>
+        <v>54665.322258438733</v>
+      </c>
+      <c r="G29" s="226">
         <f t="shared" si="0"/>
-        <v>25590.323225268006</v>
+        <v>0</v>
       </c>
       <c r="H29" s="56">
         <f t="shared" si="1"/>
-        <v>1023.6129290107202</v>
+        <v>0</v>
       </c>
       <c r="I29" s="56">
         <f t="shared" si="2"/>
-        <v>13366.5531156</v>
+        <v>23294.233551600002</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
-        <v>3884.8329885600006</v>
+        <v>7517.8171969199993</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" si="3"/>
@@ -3868,18 +3814,18 @@
       </c>
       <c r="L29" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="M29" s="57">
         <f t="shared" si="5"/>
-        <v>54665.322258438733</v>
-      </c>
-      <c r="O29" s="151">
+        <v>30812.05074852</v>
+      </c>
+      <c r="O29" s="146">
         <f t="shared" si="6"/>
-        <v>50780.48926987873</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>23294.233551600002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="67"/>
       <c r="B30" s="67"/>
       <c r="C30" s="68"/>
@@ -3894,7 +3840,7 @@
       <c r="L30" s="71"/>
       <c r="M30" s="71"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="72"/>
       <c r="B31" s="73"/>
       <c r="C31" s="74" t="s">
@@ -3905,93 +3851,93 @@
         <v>99.999999999999986</v>
       </c>
       <c r="E31" s="73"/>
-      <c r="F31" s="135">
+      <c r="F31" s="132">
         <f>SUM(F3:F30)</f>
-        <v>2466028.3590707099</v>
+        <v>2899814.6830321611</v>
       </c>
       <c r="G31" s="75"/>
       <c r="H31" s="75"/>
-      <c r="I31" s="136">
+      <c r="I31" s="133">
         <f>SUM(I3:I30)</f>
-        <v>1237643.8070000003</v>
-      </c>
-      <c r="J31" s="136"/>
-      <c r="K31" s="136">
+        <v>2156873.477</v>
+      </c>
+      <c r="J31" s="133"/>
+      <c r="K31" s="133">
         <f>SUM(K3:K30)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="135"/>
-      <c r="M31" s="135">
+      <c r="L31" s="132"/>
+      <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>3398007.4200824555</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>3698857.839265076</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="228" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="228"/>
-      <c r="C33" s="228"/>
-      <c r="D33" s="228"/>
-      <c r="E33" s="228"/>
-      <c r="F33" s="228"/>
-      <c r="G33" s="228"/>
-      <c r="H33" s="228"/>
-      <c r="I33" s="228"/>
-      <c r="J33" s="228"/>
-      <c r="K33" s="228"/>
-      <c r="L33" s="228"/>
-      <c r="M33" s="228"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="228"/>
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="228"/>
-      <c r="I34" s="228"/>
-      <c r="J34" s="228"/>
-      <c r="K34" s="228"/>
-      <c r="L34" s="228"/>
-      <c r="M34" s="228"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="228"/>
-      <c r="B35" s="228"/>
-      <c r="C35" s="228"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="228"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="228"/>
-      <c r="L35" s="228"/>
-      <c r="M35" s="228"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="228"/>
-      <c r="B36" s="228"/>
-      <c r="C36" s="228"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="228"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="228"/>
-      <c r="L36" s="228"/>
-      <c r="M36" s="228"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="215" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="215"/>
+      <c r="C33" s="215"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+      <c r="I33" s="215"/>
+      <c r="J33" s="215"/>
+      <c r="K33" s="215"/>
+      <c r="L33" s="215"/>
+      <c r="M33" s="215"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="215"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="215"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="215"/>
+      <c r="G34" s="215"/>
+      <c r="H34" s="215"/>
+      <c r="I34" s="215"/>
+      <c r="J34" s="215"/>
+      <c r="K34" s="215"/>
+      <c r="L34" s="215"/>
+      <c r="M34" s="215"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="215"/>
+      <c r="B35" s="215"/>
+      <c r="C35" s="215"/>
+      <c r="D35" s="215"/>
+      <c r="E35" s="215"/>
+      <c r="F35" s="215"/>
+      <c r="G35" s="215"/>
+      <c r="H35" s="215"/>
+      <c r="I35" s="215"/>
+      <c r="J35" s="215"/>
+      <c r="K35" s="215"/>
+      <c r="L35" s="215"/>
+      <c r="M35" s="215"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="215"/>
+      <c r="B36" s="215"/>
+      <c r="C36" s="215"/>
+      <c r="D36" s="215"/>
+      <c r="E36" s="215"/>
+      <c r="F36" s="215"/>
+      <c r="G36" s="215"/>
+      <c r="H36" s="215"/>
+      <c r="I36" s="215"/>
+      <c r="J36" s="215"/>
+      <c r="K36" s="215"/>
+      <c r="L36" s="215"/>
+      <c r="M36" s="215"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
     </row>
   </sheetData>
@@ -4011,167 +3957,163 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="231" t="s">
+    <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="218" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="232"/>
-      <c r="M1" s="232"/>
-      <c r="N1" s="233"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
       <c r="O1" s="76"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="77"/>
       <c r="B2" s="77"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="162"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-      <c r="L2" s="161"/>
-      <c r="M2" s="161"/>
-      <c r="N2" s="161"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156"/>
+      <c r="L2" s="156"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="156"/>
       <c r="O2" s="78"/>
       <c r="P2" s="11"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="80"/>
       <c r="B3" s="80"/>
-      <c r="C3" s="163"/>
-      <c r="D3" s="163"/>
-      <c r="E3" s="163"/>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="162"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-      <c r="L3" s="161"/>
-      <c r="M3" s="161"/>
-      <c r="N3" s="161"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="156"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="156"/>
       <c r="O3" s="78"/>
       <c r="P3" s="11"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="80"/>
       <c r="B4" s="80"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="163"/>
-      <c r="F4" s="163"/>
-      <c r="G4" s="163"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="161" t="s">
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="157"/>
+      <c r="I4" s="156" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="156"/>
+      <c r="L4" s="156"/>
+      <c r="M4" s="156"/>
+      <c r="N4" s="156"/>
       <c r="O4" s="78"/>
       <c r="P4" s="11"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
-      <c r="C5" s="163"/>
-      <c r="D5" s="163"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="163"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="156"/>
+      <c r="J5" s="156"/>
+      <c r="K5" s="156"/>
+      <c r="L5" s="156"/>
+      <c r="M5" s="156"/>
+      <c r="N5" s="156"/>
       <c r="O5" s="78"/>
       <c r="P5" s="11"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="80"/>
       <c r="B6" s="80"/>
-      <c r="C6" s="209" t="str">
+      <c r="C6" s="201" t="str">
         <f>'detalle y gastos'!C7</f>
-        <v>Vto. 16/01</v>
+        <v>Vto. 16/02</v>
       </c>
       <c r="D6" s="28"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="162"/>
-      <c r="I6" s="161"/>
-      <c r="J6" s="161"/>
-      <c r="K6" s="161"/>
-      <c r="L6" s="161"/>
-      <c r="M6" s="161"/>
-      <c r="N6" s="161"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="156"/>
+      <c r="K6" s="156"/>
+      <c r="L6" s="156"/>
+      <c r="M6" s="156"/>
+      <c r="N6" s="156"/>
       <c r="O6" s="78"/>
       <c r="P6" s="11"/>
     </row>
-    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="81"/>
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="212">
-        <v>666521.55000000005</v>
+      <c r="C7" s="224">
+        <f>-'detalle y gastos'!C50</f>
+        <v>1018468.24</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="161"/>
-      <c r="F7" s="161" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="161"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161" t="str">
-        <f>'detalle y gastos'!C7</f>
-        <v>Vto. 16/01</v>
-      </c>
-      <c r="K7" s="161"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="156"/>
+      <c r="L7" s="156"/>
+      <c r="M7" s="156"/>
+      <c r="N7" s="156"/>
       <c r="O7" s="78"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="81"/>
       <c r="B8" s="80" t="s">
         <v>77</v>
@@ -4183,1495 +4125,1494 @@
       <c r="H8" s="83"/>
       <c r="I8" s="82"/>
       <c r="J8" s="78"/>
-      <c r="K8" s="86">
+      <c r="K8" s="222">
         <f>C8-J38</f>
-        <v>-306814.79180000001</v>
-      </c>
-      <c r="L8" s="235">
+        <v>-322374.05510000011</v>
+      </c>
+      <c r="L8" s="223">
         <f>C7-J38</f>
-        <v>359706.75820000004</v>
-      </c>
-      <c r="M8" s="235"/>
+        <v>696094.18489999988</v>
+      </c>
+      <c r="M8" s="223"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
     </row>
-    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="s">
+    <row r="9" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="119" t="s">
+      <c r="C9" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="120" t="s">
+      <c r="D9" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="118" t="s">
+      <c r="F9" s="116" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="118" t="s">
+      <c r="G9" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="121" t="s">
+      <c r="H9" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="122" t="s">
+      <c r="I9" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="J9" s="123" t="s">
+      <c r="J9" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="124" t="s">
+      <c r="K9" s="232" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="124" t="s">
+      <c r="L9" s="232" t="s">
         <v>84</v>
       </c>
-      <c r="M9" s="125" t="s">
+      <c r="M9" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="N9" s="118" t="s">
+      <c r="N9" s="116" t="s">
         <v>86</v>
       </c>
       <c r="P9" s="11"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="98">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="97">
         <v>1</v>
       </c>
-      <c r="B10" s="88">
+      <c r="B10" s="87">
         <v>1</v>
       </c>
-      <c r="C10" s="115" t="s">
+      <c r="C10" s="113" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="100" t="s">
+      <c r="D10" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="100">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F10" s="103">
-        <v>4441.7</v>
-      </c>
-      <c r="G10" s="103">
+      <c r="F10" s="102">
         <v>4657.8999999999996</v>
       </c>
-      <c r="H10" s="104">
+      <c r="G10" s="102">
+        <v>4893.5</v>
+      </c>
+      <c r="H10" s="103">
         <f>G10-F10</f>
-        <v>216.19999999999982</v>
-      </c>
-      <c r="I10" s="105">
+        <v>235.60000000000036</v>
+      </c>
+      <c r="I10" s="104">
         <f t="shared" ref="I10:I37" si="0">H10*7%</f>
-        <v>15.133999999999988</v>
-      </c>
-      <c r="J10" s="116">
+        <v>16.492000000000026</v>
+      </c>
+      <c r="J10" s="114">
         <f>M10*93.787</f>
-        <v>20276.749399999986</v>
-      </c>
-      <c r="K10" s="106">
+        <v>22096.217200000036</v>
+      </c>
+      <c r="K10" s="114">
         <f>K8*E10%</f>
-        <v>-15678.235860980003</v>
-      </c>
-      <c r="L10" s="127">
+        <v>-16473.314215610008</v>
+      </c>
+      <c r="L10" s="235">
         <f>L$8*E10/S$12</f>
-        <v>18381.015344020001</v>
-      </c>
-      <c r="M10" s="107">
+        <v>35570.412848389999</v>
+      </c>
+      <c r="M10" s="105">
         <f>G10-F10</f>
-        <v>216.19999999999982</v>
-      </c>
-      <c r="N10" s="104">
+        <v>235.60000000000036</v>
+      </c>
+      <c r="N10" s="103">
         <f>J10+L10</f>
-        <v>38657.764744019987</v>
-      </c>
-      <c r="O10" s="97">
+        <v>57666.630048390034</v>
+      </c>
+      <c r="O10" s="96">
         <f>N10+'prorrateo '!M3</f>
-        <v>191659.12802573998</v>
+        <v>225549.49477148007</v>
       </c>
       <c r="P10" s="11"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="99">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="98">
         <v>2</v>
       </c>
-      <c r="B11" s="89">
+      <c r="B11" s="88">
         <v>2</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="100" t="s">
+      <c r="D11" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="101">
+      <c r="E11" s="100">
         <v>5.09</v>
       </c>
-      <c r="F11" s="103">
-        <v>4207.8</v>
-      </c>
-      <c r="G11" s="103">
+      <c r="F11" s="102">
         <v>4378</v>
       </c>
-      <c r="H11" s="104">
+      <c r="G11" s="102">
+        <v>4543.8</v>
+      </c>
+      <c r="H11" s="103">
         <f t="shared" ref="H11:H27" si="1">G11-F11</f>
-        <v>170.19999999999982</v>
-      </c>
-      <c r="I11" s="105">
+        <v>165.80000000000018</v>
+      </c>
+      <c r="I11" s="104">
         <f t="shared" si="0"/>
-        <v>11.913999999999989</v>
-      </c>
-      <c r="J11" s="116">
+        <v>11.606000000000014</v>
+      </c>
+      <c r="J11" s="114">
         <f t="shared" ref="J11:J26" si="2">M11*93.787</f>
-        <v>15962.547399999983</v>
-      </c>
-      <c r="K11" s="106">
+        <v>15549.884600000018</v>
+      </c>
+      <c r="K11" s="114">
         <f>K8*E11%</f>
-        <v>-15616.87290262</v>
-      </c>
-      <c r="L11" s="127">
+        <v>-16408.839404590006</v>
+      </c>
+      <c r="L11" s="235">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
-        <v>18309.073992380003</v>
-      </c>
-      <c r="M11" s="107">
+        <v>35431.194011409993</v>
+      </c>
+      <c r="M11" s="105">
         <f t="shared" ref="M11:M26" si="4">G11-F11</f>
-        <v>170.19999999999982</v>
-      </c>
-      <c r="N11" s="104">
+        <v>165.80000000000018</v>
+      </c>
+      <c r="N11" s="103">
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
-        <v>34271.621392379988</v>
-      </c>
-      <c r="O11" s="97">
+        <v>50981.078611410012</v>
+      </c>
+      <c r="O11" s="96">
         <f>N11+'prorrateo '!M4</f>
-        <v>182439.31256105995</v>
+        <v>211747.01720212004</v>
       </c>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="98">
+    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="97">
         <v>3</v>
       </c>
-      <c r="B12" s="89">
+      <c r="B12" s="88">
         <v>3</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="100" t="s">
+      <c r="D12" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="101">
+      <c r="E12" s="100">
         <v>5.04</v>
       </c>
-      <c r="F12" s="103">
-        <v>1667.5</v>
-      </c>
-      <c r="G12" s="103">
+      <c r="F12" s="102">
         <v>1981.8</v>
       </c>
-      <c r="H12" s="104">
+      <c r="G12" s="102">
+        <v>2352.9</v>
+      </c>
+      <c r="H12" s="103">
         <f t="shared" si="1"/>
-        <v>314.29999999999995</v>
-      </c>
-      <c r="I12" s="105">
+        <v>371.10000000000014</v>
+      </c>
+      <c r="I12" s="104">
         <f t="shared" si="0"/>
-        <v>22.000999999999998</v>
-      </c>
-      <c r="J12" s="116">
+        <v>25.977000000000011</v>
+      </c>
+      <c r="J12" s="114">
         <f t="shared" si="2"/>
-        <v>29477.254099999998</v>
-      </c>
-      <c r="K12" s="106">
+        <v>34804.355700000015</v>
+      </c>
+      <c r="K12" s="114">
         <f>K8*E12%</f>
-        <v>-15463.46550672</v>
-      </c>
-      <c r="L12" s="127">
+        <v>-16247.652377040005</v>
+      </c>
+      <c r="L12" s="235">
         <f t="shared" si="3"/>
-        <v>18129.220613280002</v>
-      </c>
-      <c r="M12" s="107">
+        <v>35083.146918959996</v>
+      </c>
+      <c r="M12" s="105">
         <f>G12-F12</f>
-        <v>314.29999999999995</v>
-      </c>
-      <c r="N12" s="104">
+        <v>371.10000000000014</v>
+      </c>
+      <c r="N12" s="103">
         <f t="shared" si="5"/>
-        <v>47606.474713279997</v>
-      </c>
-      <c r="O12" s="97">
+        <v>69887.502618960018</v>
+      </c>
+      <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>235359.93146704871</v>
+        <v>248481.42133664872</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="98">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="97">
         <v>4</v>
       </c>
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="164" t="s">
+      <c r="C13" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="100" t="s">
+      <c r="D13" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="165">
+      <c r="E13" s="160">
         <v>5.21</v>
       </c>
-      <c r="F13" s="103">
-        <v>1283.0999999999999</v>
-      </c>
-      <c r="G13" s="103">
+      <c r="F13" s="102">
         <v>1453</v>
       </c>
-      <c r="H13" s="104">
+      <c r="G13" s="102">
+        <v>1511.5</v>
+      </c>
+      <c r="H13" s="103">
         <f t="shared" si="1"/>
-        <v>169.90000000000009</v>
-      </c>
-      <c r="I13" s="166">
+        <v>58.5</v>
+      </c>
+      <c r="I13" s="161">
         <f t="shared" si="0"/>
-        <v>11.893000000000008</v>
-      </c>
-      <c r="J13" s="116">
+        <v>4.0950000000000006</v>
+      </c>
+      <c r="J13" s="114">
         <f t="shared" si="2"/>
-        <v>15934.411300000009</v>
-      </c>
-      <c r="K13" s="167">
+        <v>5486.5395000000008</v>
+      </c>
+      <c r="K13" s="236">
         <f>K8*E13%</f>
-        <v>-15985.050652780001</v>
-      </c>
-      <c r="L13" s="127">
+        <v>-16795.688270710005</v>
+      </c>
+      <c r="L13" s="235">
         <f t="shared" si="3"/>
-        <v>18740.722102220003</v>
-      </c>
-      <c r="M13" s="168">
+        <v>36266.507033289992</v>
+      </c>
+      <c r="M13" s="162">
         <f t="shared" si="4"/>
-        <v>169.90000000000009</v>
-      </c>
-      <c r="N13" s="104">
+        <v>58.5</v>
+      </c>
+      <c r="N13" s="103">
         <f t="shared" si="5"/>
-        <v>34675.13340222001</v>
-      </c>
-      <c r="O13" s="97">
+        <v>41753.046533289991</v>
+      </c>
+      <c r="O13" s="96">
         <f>N13+'prorrateo '!M6</f>
-        <v>185931.50914914001</v>
+        <v>353185.83199507679</v>
       </c>
       <c r="P13" s="11"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="98">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="97">
         <v>6</v>
       </c>
-      <c r="B14" s="89">
+      <c r="B14" s="88">
         <v>6</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="100" t="s">
+      <c r="D14" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="101">
+      <c r="E14" s="100">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F14" s="103">
-        <v>1914.3</v>
-      </c>
-      <c r="G14" s="103">
+      <c r="F14" s="102">
         <v>2130</v>
       </c>
-      <c r="H14" s="104">
+      <c r="G14" s="102">
+        <v>2363.6</v>
+      </c>
+      <c r="H14" s="103">
         <f t="shared" si="1"/>
-        <v>215.70000000000005</v>
-      </c>
-      <c r="I14" s="105">
+        <v>233.59999999999991</v>
+      </c>
+      <c r="I14" s="104">
         <f t="shared" si="0"/>
-        <v>15.099000000000004</v>
-      </c>
-      <c r="J14" s="116">
+        <v>16.351999999999997</v>
+      </c>
+      <c r="J14" s="114">
         <f t="shared" si="2"/>
-        <v>20229.855900000006</v>
-      </c>
-      <c r="K14" s="106">
+        <v>21908.643199999991</v>
+      </c>
+      <c r="K14" s="114">
         <f>K8*E14%</f>
-        <v>-15678.235860980003</v>
-      </c>
-      <c r="L14" s="127">
+        <v>-16473.314215610008</v>
+      </c>
+      <c r="L14" s="235">
         <f t="shared" si="3"/>
-        <v>18381.015344020001</v>
-      </c>
-      <c r="M14" s="107">
+        <v>35570.412848389999</v>
+      </c>
+      <c r="M14" s="105">
         <f t="shared" si="4"/>
-        <v>215.70000000000005</v>
-      </c>
-      <c r="N14" s="104">
+        <v>233.59999999999991</v>
+      </c>
+      <c r="N14" s="103">
         <f t="shared" si="5"/>
-        <v>38610.871244020003</v>
-      </c>
-      <c r="O14" s="97">
+        <v>57479.05604838999</v>
+      </c>
+      <c r="O14" s="96">
         <f>N14+'prorrateo '!M7</f>
-        <v>191565.34102574002</v>
+        <v>225174.34265736002</v>
       </c>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="98">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="97">
         <v>7</v>
       </c>
-      <c r="B15" s="89">
+      <c r="B15" s="88">
         <v>7</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="100" t="s">
+      <c r="D15" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="101">
+      <c r="E15" s="100">
         <v>5.09</v>
       </c>
-      <c r="F15" s="103">
-        <v>3098.9</v>
-      </c>
-      <c r="G15" s="103">
+      <c r="F15" s="102">
         <v>3326.8</v>
       </c>
-      <c r="H15" s="104">
+      <c r="G15" s="102">
+        <v>3564.3</v>
+      </c>
+      <c r="H15" s="103">
         <f t="shared" si="1"/>
-        <v>227.90000000000009</v>
-      </c>
-      <c r="I15" s="105">
+        <v>237.5</v>
+      </c>
+      <c r="I15" s="104">
         <f t="shared" si="0"/>
-        <v>15.953000000000008</v>
-      </c>
-      <c r="J15" s="116">
+        <v>16.625</v>
+      </c>
+      <c r="J15" s="114">
         <f t="shared" si="2"/>
-        <v>21374.057300000011</v>
-      </c>
-      <c r="K15" s="106">
+        <v>22274.412500000002</v>
+      </c>
+      <c r="K15" s="114">
         <f>K8*E15%</f>
-        <v>-15616.87290262</v>
-      </c>
-      <c r="L15" s="127">
+        <v>-16408.839404590006</v>
+      </c>
+      <c r="L15" s="235">
         <f t="shared" si="3"/>
-        <v>18309.073992380003</v>
-      </c>
-      <c r="M15" s="107">
+        <v>35431.194011409993</v>
+      </c>
+      <c r="M15" s="105">
         <f t="shared" si="4"/>
-        <v>227.90000000000009</v>
-      </c>
-      <c r="N15" s="104">
+        <v>237.5</v>
+      </c>
+      <c r="N15" s="103">
         <f t="shared" si="5"/>
-        <v>39683.131292380014</v>
-      </c>
-      <c r="O15" s="97">
+        <v>57705.606511409991</v>
+      </c>
+      <c r="O15" s="96">
         <f>N15+'prorrateo '!M8</f>
-        <v>193262.33236106002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="98">
+        <v>225196.07300211996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="97">
         <v>8</v>
       </c>
-      <c r="B16" s="89">
+      <c r="B16" s="88">
         <v>8</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="100" t="s">
+      <c r="D16" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="101">
+      <c r="E16" s="100">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F16" s="103">
-        <v>2607.6</v>
-      </c>
-      <c r="G16" s="103">
+      <c r="F16" s="102">
         <v>2744.5</v>
       </c>
-      <c r="H16" s="104">
+      <c r="G16" s="102">
+        <v>2836.7</v>
+      </c>
+      <c r="H16" s="103">
         <f t="shared" si="1"/>
-        <v>136.90000000000009</v>
-      </c>
-      <c r="I16" s="105">
+        <v>92.199999999999818</v>
+      </c>
+      <c r="I16" s="104">
         <f t="shared" si="0"/>
-        <v>9.5830000000000073</v>
-      </c>
-      <c r="J16" s="116">
+        <v>6.4539999999999882</v>
+      </c>
+      <c r="J16" s="114">
         <f t="shared" si="2"/>
-        <v>12839.440300000009</v>
-      </c>
-      <c r="K16" s="106">
+        <v>8647.1613999999827</v>
+      </c>
+      <c r="K16" s="114">
         <f>K8*E16%</f>
-        <v>-15678.235860980003</v>
-      </c>
-      <c r="L16" s="127">
+        <v>-16473.314215610008</v>
+      </c>
+      <c r="L16" s="235">
         <f t="shared" si="3"/>
-        <v>18381.015344020001</v>
-      </c>
-      <c r="M16" s="107">
+        <v>35570.412848389999</v>
+      </c>
+      <c r="M16" s="105">
         <f t="shared" si="4"/>
-        <v>136.90000000000009</v>
-      </c>
-      <c r="N16" s="104">
+        <v>92.199999999999818</v>
+      </c>
+      <c r="N16" s="103">
         <f t="shared" si="5"/>
-        <v>31220.45564402001</v>
-      </c>
-      <c r="O16" s="97">
+        <v>44217.574248389981</v>
+      </c>
+      <c r="O16" s="96">
         <f>N16+'prorrateo '!M9</f>
-        <v>176418.02467122104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="98">
+        <v>198651.38317147997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="97">
         <v>9</v>
       </c>
-      <c r="B17" s="89">
+      <c r="B17" s="88">
         <v>9</v>
       </c>
-      <c r="C17" s="185" t="s">
+      <c r="C17" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="186" t="s">
+      <c r="D17" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="187">
+      <c r="E17" s="181">
         <v>5.09</v>
       </c>
-      <c r="F17" s="188">
-        <v>3400.1</v>
-      </c>
-      <c r="G17" s="188">
+      <c r="F17" s="182">
         <v>3430.2</v>
       </c>
-      <c r="H17" s="189">
+      <c r="G17" s="182">
+        <v>3459.5</v>
+      </c>
+      <c r="H17" s="183">
         <f t="shared" si="1"/>
-        <v>30.099999999999909</v>
-      </c>
-      <c r="I17" s="190">
+        <v>29.300000000000182</v>
+      </c>
+      <c r="I17" s="184">
         <f t="shared" si="0"/>
-        <v>2.106999999999994</v>
-      </c>
-      <c r="J17" s="191">
+        <v>2.051000000000013</v>
+      </c>
+      <c r="J17" s="185">
         <f t="shared" si="2"/>
-        <v>2822.9886999999917</v>
-      </c>
-      <c r="K17" s="192">
+        <v>2747.9591000000173</v>
+      </c>
+      <c r="K17" s="185">
         <f>K8*E17%</f>
-        <v>-15616.87290262</v>
-      </c>
-      <c r="L17" s="193">
+        <v>-16408.839404590006</v>
+      </c>
+      <c r="L17" s="237">
         <f t="shared" si="3"/>
-        <v>18309.073992380003</v>
-      </c>
-      <c r="M17" s="194">
+        <v>35431.194011409993</v>
+      </c>
+      <c r="M17" s="186">
         <f t="shared" si="4"/>
-        <v>30.099999999999909</v>
-      </c>
-      <c r="N17" s="189">
+        <v>29.300000000000182</v>
+      </c>
+      <c r="N17" s="183">
         <f t="shared" si="5"/>
-        <v>21132.062692379994</v>
-      </c>
-      <c r="O17" s="97">
+        <v>38179.153111410007</v>
+      </c>
+      <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>156160.19516105996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="98">
+        <v>186143.16620212002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="97">
         <v>10</v>
       </c>
-      <c r="B18" s="89">
+      <c r="B18" s="88">
         <v>10</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="100" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="101">
+      <c r="D18" s="99" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="100">
         <v>5.04</v>
       </c>
-      <c r="F18" s="103">
-        <v>2354.6999999999998</v>
-      </c>
-      <c r="G18" s="103">
+      <c r="F18" s="102">
         <v>2485.1</v>
       </c>
-      <c r="H18" s="104">
+      <c r="G18" s="102">
+        <v>2601.9</v>
+      </c>
+      <c r="H18" s="103">
         <f t="shared" si="1"/>
-        <v>130.40000000000009</v>
-      </c>
-      <c r="I18" s="105">
+        <v>116.80000000000018</v>
+      </c>
+      <c r="I18" s="104">
         <f t="shared" si="0"/>
-        <v>9.1280000000000072</v>
-      </c>
-      <c r="J18" s="116">
+        <v>8.1760000000000144</v>
+      </c>
+      <c r="J18" s="114">
         <f t="shared" si="2"/>
-        <v>12229.824800000009</v>
-      </c>
-      <c r="K18" s="106">
+        <v>10954.321600000017</v>
+      </c>
+      <c r="K18" s="114">
         <f>K8*E18%</f>
-        <v>-15463.46550672</v>
-      </c>
-      <c r="L18" s="127">
+        <v>-16247.652377040005</v>
+      </c>
+      <c r="L18" s="235">
         <f t="shared" si="3"/>
-        <v>18129.220613280002</v>
-      </c>
-      <c r="M18" s="107">
+        <v>35083.146918959996</v>
+      </c>
+      <c r="M18" s="105">
         <f t="shared" si="4"/>
-        <v>130.40000000000009</v>
-      </c>
-      <c r="N18" s="104">
+        <v>116.80000000000018</v>
+      </c>
+      <c r="N18" s="103">
         <f t="shared" si="5"/>
-        <v>30359.045413280011</v>
-      </c>
-      <c r="O18" s="97">
+        <v>46037.468518960013</v>
+      </c>
+      <c r="O18" s="96">
         <f>N18+'prorrateo '!M11</f>
-        <v>173495.33869936003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="98">
+        <v>349643.10529624321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="97">
         <v>11</v>
       </c>
-      <c r="B19" s="89">
+      <c r="B19" s="88">
         <v>11</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="108" t="s">
+      <c r="D19" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="101">
+      <c r="E19" s="100">
         <v>5.21</v>
       </c>
-      <c r="F19" s="103">
-        <v>4574.8999999999996</v>
-      </c>
-      <c r="G19" s="103">
+      <c r="F19" s="102">
         <v>4913.8</v>
       </c>
-      <c r="H19" s="104">
+      <c r="G19" s="102">
+        <v>5191</v>
+      </c>
+      <c r="H19" s="103">
         <f t="shared" si="1"/>
-        <v>338.90000000000055</v>
-      </c>
-      <c r="I19" s="105">
+        <v>277.19999999999982</v>
+      </c>
+      <c r="I19" s="104">
         <f t="shared" si="0"/>
-        <v>23.723000000000042</v>
-      </c>
-      <c r="J19" s="116">
+        <v>19.403999999999989</v>
+      </c>
+      <c r="J19" s="114">
         <f t="shared" si="2"/>
-        <v>31784.414300000055</v>
-      </c>
-      <c r="K19" s="106">
+        <v>25997.756399999984</v>
+      </c>
+      <c r="K19" s="114">
         <f>K8*E19%</f>
-        <v>-15985.050652780001</v>
-      </c>
-      <c r="L19" s="127">
+        <v>-16795.688270710005</v>
+      </c>
+      <c r="L19" s="235">
         <f t="shared" si="3"/>
-        <v>18740.722102220003</v>
-      </c>
-      <c r="M19" s="107">
+        <v>36266.507033289992</v>
+      </c>
+      <c r="M19" s="105">
         <f>G19-F19</f>
-        <v>338.90000000000055</v>
-      </c>
-      <c r="N19" s="104">
+        <v>277.19999999999982</v>
+      </c>
+      <c r="N19" s="103">
         <f t="shared" si="5"/>
-        <v>50525.136402220058</v>
-      </c>
-      <c r="O19" s="97">
+        <v>62264.263433289976</v>
+      </c>
+      <c r="O19" s="96">
         <f>N19+'prorrateo '!M12</f>
-        <v>217631.51514914012</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="98">
+        <v>236901.63501827995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="97">
         <v>12</v>
       </c>
-      <c r="B20" s="89">
+      <c r="B20" s="88">
         <v>12</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="108" t="s">
+      <c r="D20" s="106" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="101">
+      <c r="E20" s="100">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F20" s="103">
-        <v>6064.7</v>
-      </c>
-      <c r="G20" s="103">
+      <c r="F20" s="102">
         <v>6379</v>
       </c>
-      <c r="H20" s="104">
+      <c r="G20" s="102">
+        <v>6705</v>
+      </c>
+      <c r="H20" s="103">
         <f t="shared" si="1"/>
-        <v>314.30000000000018</v>
-      </c>
-      <c r="I20" s="105">
+        <v>326</v>
+      </c>
+      <c r="I20" s="104">
         <f t="shared" si="0"/>
-        <v>22.001000000000015</v>
-      </c>
-      <c r="J20" s="116">
+        <v>22.820000000000004</v>
+      </c>
+      <c r="J20" s="114">
         <f t="shared" si="2"/>
-        <v>29477.25410000002</v>
-      </c>
-      <c r="K20" s="106">
+        <v>30574.562000000002</v>
+      </c>
+      <c r="K20" s="114">
         <f>K8*E20%</f>
-        <v>-15678.235860980003</v>
-      </c>
-      <c r="L20" s="127">
+        <v>-16473.314215610008</v>
+      </c>
+      <c r="L20" s="235">
         <f t="shared" si="3"/>
-        <v>18381.015344020001</v>
-      </c>
-      <c r="M20" s="107">
+        <v>35570.412848389999</v>
+      </c>
+      <c r="M20" s="105">
         <f t="shared" si="4"/>
-        <v>314.30000000000018</v>
-      </c>
-      <c r="N20" s="104">
+        <v>326</v>
+      </c>
+      <c r="N20" s="103">
         <f t="shared" si="5"/>
-        <v>47858.269444020021</v>
-      </c>
-      <c r="O20" s="97">
+        <v>66144.974848390004</v>
+      </c>
+      <c r="O20" s="96">
         <f>N20+'prorrateo '!M13</f>
-        <v>210060.13742574007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="98">
+        <v>242506.17845736005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="97">
         <v>13</v>
       </c>
-      <c r="B21" s="89">
+      <c r="B21" s="88">
         <v>13</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="100" t="s">
+      <c r="D21" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="101">
+      <c r="E21" s="100">
         <v>5.09</v>
       </c>
-      <c r="F21" s="103">
-        <v>4199</v>
-      </c>
-      <c r="G21" s="103">
+      <c r="F21" s="102">
         <v>4271.8</v>
       </c>
-      <c r="H21" s="104">
+      <c r="G21" s="102">
+        <v>4338.3</v>
+      </c>
+      <c r="H21" s="103">
         <f t="shared" si="1"/>
-        <v>72.800000000000182</v>
-      </c>
-      <c r="I21" s="105">
+        <v>66.5</v>
+      </c>
+      <c r="I21" s="104">
         <f t="shared" si="0"/>
-        <v>5.0960000000000134</v>
-      </c>
-      <c r="J21" s="116">
+        <v>4.6550000000000002</v>
+      </c>
+      <c r="J21" s="114">
         <f t="shared" si="2"/>
-        <v>6827.6936000000178</v>
-      </c>
-      <c r="K21" s="106">
+        <v>6236.8355000000001</v>
+      </c>
+      <c r="K21" s="114">
         <f>K8*E21%</f>
-        <v>-15616.87290262</v>
-      </c>
-      <c r="L21" s="127">
+        <v>-16408.839404590006</v>
+      </c>
+      <c r="L21" s="235">
         <f t="shared" si="3"/>
-        <v>18309.073992380003</v>
-      </c>
-      <c r="M21" s="107">
+        <v>35431.194011409993</v>
+      </c>
+      <c r="M21" s="105">
         <f t="shared" si="4"/>
-        <v>72.800000000000182</v>
-      </c>
-      <c r="N21" s="104">
+        <v>66.5</v>
+      </c>
+      <c r="N21" s="103">
         <f t="shared" si="5"/>
-        <v>25136.76759238002</v>
-      </c>
-      <c r="O21" s="97">
+        <v>41668.029511409994</v>
+      </c>
+      <c r="O21" s="96">
         <f>N21+'prorrateo '!M14</f>
-        <v>164132.47985636702</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="98">
+        <v>193121.00050499284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="97">
         <v>14</v>
       </c>
-      <c r="B22" s="89">
+      <c r="B22" s="88">
         <v>14</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="100" t="s">
+      <c r="D22" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="101">
+      <c r="E22" s="100">
         <v>5.04</v>
       </c>
-      <c r="F22" s="103">
-        <v>2497.1</v>
-      </c>
-      <c r="G22" s="103">
+      <c r="F22" s="102">
         <v>2698.4</v>
       </c>
-      <c r="H22" s="104">
+      <c r="G22" s="102">
+        <v>2797.6</v>
+      </c>
+      <c r="H22" s="103">
         <f t="shared" si="1"/>
-        <v>201.30000000000018</v>
-      </c>
-      <c r="I22" s="105">
+        <v>99.199999999999818</v>
+      </c>
+      <c r="I22" s="104">
         <f t="shared" si="0"/>
-        <v>14.091000000000014</v>
-      </c>
-      <c r="J22" s="116">
+        <v>6.9439999999999875</v>
+      </c>
+      <c r="J22" s="114">
         <f t="shared" si="2"/>
-        <v>18879.32310000002</v>
-      </c>
-      <c r="K22" s="106">
+        <v>9303.6703999999827</v>
+      </c>
+      <c r="K22" s="114">
         <f>K8*E22%</f>
-        <v>-15463.46550672</v>
-      </c>
-      <c r="L22" s="127">
+        <v>-16247.652377040005</v>
+      </c>
+      <c r="L22" s="235">
         <f t="shared" si="3"/>
-        <v>18129.220613280002</v>
-      </c>
-      <c r="M22" s="107">
+        <v>35083.146918959996</v>
+      </c>
+      <c r="M22" s="105">
         <f t="shared" si="4"/>
-        <v>201.30000000000018</v>
-      </c>
-      <c r="N22" s="104">
+        <v>99.199999999999818</v>
+      </c>
+      <c r="N22" s="103">
         <f t="shared" si="5"/>
-        <v>37008.543713280022</v>
-      </c>
-      <c r="O22" s="97">
+        <v>44386.817318959977</v>
+      </c>
+      <c r="O22" s="96">
         <f>N22+'prorrateo '!M15</f>
-        <v>316415.8483230432</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="98">
+        <v>197480.06502164999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="97">
         <v>15</v>
       </c>
-      <c r="B23" s="89">
+      <c r="B23" s="88">
         <v>15</v>
       </c>
-      <c r="C23" s="115" t="s">
+      <c r="C23" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="100" t="s">
+      <c r="D23" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="101">
+      <c r="E23" s="100">
         <v>5.21</v>
       </c>
-      <c r="F23" s="103">
-        <v>5000</v>
-      </c>
-      <c r="G23" s="103">
+      <c r="F23" s="102">
         <v>5255.9</v>
       </c>
-      <c r="H23" s="104">
+      <c r="G23" s="102">
+        <v>5576.5</v>
+      </c>
+      <c r="H23" s="103">
         <f t="shared" si="1"/>
-        <v>255.89999999999964</v>
-      </c>
-      <c r="I23" s="105">
+        <v>320.60000000000036</v>
+      </c>
+      <c r="I23" s="104">
         <f t="shared" si="0"/>
-        <v>17.912999999999975</v>
-      </c>
-      <c r="J23" s="116">
+        <v>22.442000000000029</v>
+      </c>
+      <c r="J23" s="114">
         <f t="shared" si="2"/>
-        <v>24000.093299999968</v>
-      </c>
-      <c r="K23" s="106">
+        <v>30068.112200000036</v>
+      </c>
+      <c r="K23" s="114">
         <f>K8*E23%</f>
-        <v>-15985.050652780001</v>
-      </c>
-      <c r="L23" s="127">
+        <v>-16795.688270710005</v>
+      </c>
+      <c r="L23" s="235">
         <f t="shared" si="3"/>
-        <v>18740.722102220003</v>
-      </c>
-      <c r="M23" s="107">
+        <v>36266.507033289992</v>
+      </c>
+      <c r="M23" s="105">
         <f t="shared" si="4"/>
-        <v>255.89999999999964</v>
-      </c>
-      <c r="N23" s="104">
+        <v>320.60000000000036</v>
+      </c>
+      <c r="N23" s="103">
         <f t="shared" si="5"/>
-        <v>42740.815402219974</v>
-      </c>
-      <c r="O23" s="97">
+        <v>66334.619233290025</v>
+      </c>
+      <c r="O23" s="96">
         <f>N23+'prorrateo '!M16</f>
-        <v>202062.87314913995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="98">
+        <v>245042.34046936</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="97">
         <v>16</v>
       </c>
-      <c r="B24" s="89">
+      <c r="B24" s="88">
         <v>16</v>
       </c>
-      <c r="C24" s="115" t="s">
+      <c r="C24" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="100" t="s">
+      <c r="D24" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="101">
+      <c r="E24" s="100">
         <v>5.04</v>
       </c>
-      <c r="F24" s="103">
-        <v>1802.7</v>
-      </c>
-      <c r="G24" s="103">
+      <c r="F24" s="102">
         <v>1847.5</v>
       </c>
-      <c r="H24" s="104">
+      <c r="G24" s="102">
+        <v>1982.9</v>
+      </c>
+      <c r="H24" s="103">
         <f t="shared" si="1"/>
-        <v>44.799999999999955</v>
-      </c>
-      <c r="I24" s="105">
+        <v>135.40000000000009</v>
+      </c>
+      <c r="I24" s="104">
         <f t="shared" si="0"/>
-        <v>3.135999999999997</v>
-      </c>
-      <c r="J24" s="116">
+        <v>9.4780000000000069</v>
+      </c>
+      <c r="J24" s="114">
         <f t="shared" si="2"/>
-        <v>4201.6575999999959</v>
-      </c>
-      <c r="K24" s="106">
+        <v>12698.759800000009</v>
+      </c>
+      <c r="K24" s="114">
         <f>K8*E24%</f>
-        <v>-15463.46550672</v>
-      </c>
-      <c r="L24" s="127">
+        <v>-16247.652377040005</v>
+      </c>
+      <c r="L24" s="235">
         <f t="shared" si="3"/>
-        <v>18129.220613280002</v>
-      </c>
-      <c r="M24" s="107">
+        <v>35083.146918959996</v>
+      </c>
+      <c r="M24" s="105">
         <f t="shared" si="4"/>
-        <v>44.799999999999955</v>
-      </c>
-      <c r="N24" s="104">
+        <v>135.40000000000009</v>
+      </c>
+      <c r="N24" s="103">
         <f t="shared" si="5"/>
-        <v>22330.878213279997</v>
-      </c>
-      <c r="O24" s="97">
+        <v>47781.906718960003</v>
+      </c>
+      <c r="O24" s="96">
         <f>N24+'prorrateo '!M17</f>
-        <v>157439.00429935998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="98">
+        <v>69378.366678720005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="97">
         <v>17</v>
       </c>
-      <c r="B25" s="89">
+      <c r="B25" s="88">
         <v>17</v>
       </c>
-      <c r="C25" s="115" t="s">
+      <c r="C25" s="113" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="100" t="s">
+      <c r="D25" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="101">
+      <c r="E25" s="100">
         <v>5.21</v>
       </c>
-      <c r="F25" s="103">
-        <v>1949.4</v>
-      </c>
-      <c r="G25" s="103">
-        <f>F25+80</f>
+      <c r="F25" s="102">
         <v>2029.4</v>
       </c>
-      <c r="H25" s="104">
+      <c r="G25" s="102">
+        <v>2155.8000000000002</v>
+      </c>
+      <c r="H25" s="103">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="I25" s="105">
+        <v>126.40000000000009</v>
+      </c>
+      <c r="I25" s="104">
         <f t="shared" si="0"/>
-        <v>5.6000000000000005</v>
-      </c>
-      <c r="J25" s="116">
+        <v>8.8480000000000079</v>
+      </c>
+      <c r="J25" s="114">
         <f t="shared" si="2"/>
-        <v>7502.9600000000009</v>
-      </c>
-      <c r="K25" s="106">
+        <v>11854.67680000001</v>
+      </c>
+      <c r="K25" s="114">
         <f>K8*E25%</f>
-        <v>-15985.050652780001</v>
-      </c>
-      <c r="L25" s="127">
+        <v>-16795.688270710005</v>
+      </c>
+      <c r="L25" s="235">
         <f t="shared" si="3"/>
-        <v>18740.722102220003</v>
-      </c>
-      <c r="M25" s="107">
+        <v>36266.507033289992</v>
+      </c>
+      <c r="M25" s="105">
         <f t="shared" si="4"/>
-        <v>80</v>
-      </c>
-      <c r="N25" s="104">
+        <v>126.40000000000009</v>
+      </c>
+      <c r="N25" s="103">
         <f t="shared" si="5"/>
-        <v>26243.682102220002</v>
-      </c>
-      <c r="O25" s="97">
+        <v>48121.183833290001</v>
+      </c>
+      <c r="O25" s="96">
         <f>N25+'prorrateo '!M18</f>
-        <v>169068.60654914001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="98">
+        <v>208615.47581828001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="97">
         <v>18</v>
       </c>
-      <c r="B26" s="89">
+      <c r="B26" s="88">
         <v>18</v>
       </c>
-      <c r="C26" s="115" t="s">
+      <c r="C26" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="100" t="s">
+      <c r="D26" s="99" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="101">
+      <c r="E26" s="100">
         <v>7.4</v>
       </c>
-      <c r="F26" s="103">
-        <v>9077.1</v>
-      </c>
-      <c r="G26" s="103">
+      <c r="F26" s="102">
         <v>9428.9</v>
       </c>
-      <c r="H26" s="104">
+      <c r="G26" s="102">
+        <v>9974.5</v>
+      </c>
+      <c r="H26" s="103">
         <f t="shared" si="1"/>
-        <v>351.79999999999927</v>
-      </c>
-      <c r="I26" s="105">
+        <v>545.60000000000036</v>
+      </c>
+      <c r="I26" s="104">
         <f t="shared" si="0"/>
-        <v>24.625999999999951</v>
-      </c>
-      <c r="J26" s="116">
+        <v>38.192000000000029</v>
+      </c>
+      <c r="J26" s="114">
         <f t="shared" si="2"/>
-        <v>32994.266599999937</v>
-      </c>
-      <c r="K26" s="106">
+        <v>51170.187200000037</v>
+      </c>
+      <c r="K26" s="114">
         <f>K8*E26%</f>
-        <v>-22704.294593200004</v>
-      </c>
-      <c r="L26" s="127">
+        <v>-23855.680077400011</v>
+      </c>
+      <c r="L26" s="235">
         <f t="shared" si="3"/>
-        <v>26618.300106800001</v>
-      </c>
-      <c r="M26" s="107">
+        <v>51510.969682599993</v>
+      </c>
+      <c r="M26" s="105">
         <f t="shared" si="4"/>
-        <v>351.79999999999927</v>
-      </c>
-      <c r="N26" s="104">
+        <v>545.60000000000036</v>
+      </c>
+      <c r="N26" s="103">
         <f>J26+L26</f>
-        <v>59612.566706799938</v>
-      </c>
-      <c r="O26" s="97">
+        <v>102681.15688260003</v>
+      </c>
+      <c r="O26" s="96">
         <f>N26+'prorrateo '!M19</f>
-        <v>284810.77513159986</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="98">
+        <v>364970.95106320007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="97">
         <v>19</v>
       </c>
-      <c r="B27" s="90">
+      <c r="B27" s="89">
         <v>19</v>
       </c>
-      <c r="C27" s="195" t="s">
+      <c r="C27" s="187" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="196"/>
-      <c r="E27" s="197">
+      <c r="D27" s="188"/>
+      <c r="E27" s="189">
         <v>1.08</v>
       </c>
-      <c r="F27" s="188"/>
-      <c r="G27" s="188"/>
-      <c r="H27" s="189">
+      <c r="F27" s="182"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="183">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="190">
+      <c r="I27" s="184">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="191"/>
-      <c r="K27" s="192"/>
-      <c r="L27" s="193">
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="237">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M27" s="194">
-        <v>0</v>
-      </c>
-      <c r="N27" s="189">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M27" s="186">
+        <v>0</v>
+      </c>
+      <c r="N27" s="183">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O27" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O27" s="96">
         <f>N27+'prorrateo '!M20</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="98">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="97">
         <v>20</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="169" t="s">
+      <c r="B28" s="89"/>
+      <c r="C28" s="163" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="102"/>
-      <c r="E28" s="102">
+      <c r="D28" s="101"/>
+      <c r="E28" s="101">
         <v>1.08</v>
       </c>
-      <c r="F28" s="102"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="104">
-        <v>0</v>
-      </c>
-      <c r="I28" s="170">
+      <c r="F28" s="101"/>
+      <c r="G28" s="101"/>
+      <c r="H28" s="103">
+        <v>0</v>
+      </c>
+      <c r="I28" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="171"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="127">
+      <c r="J28" s="165"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M28" s="107">
-        <v>0</v>
-      </c>
-      <c r="N28" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M28" s="105">
+        <v>0</v>
+      </c>
+      <c r="N28" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O28" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O28" s="96">
         <f>N28+'prorrateo '!M21</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="98"/>
-      <c r="B29" s="90"/>
-      <c r="C29" s="158" t="s">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="97"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="146"/>
-      <c r="E29" s="146">
+      <c r="D29" s="143"/>
+      <c r="E29" s="143">
         <v>1.08</v>
       </c>
-      <c r="F29" s="146"/>
-      <c r="G29" s="146"/>
-      <c r="H29" s="147"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="148"/>
-      <c r="L29" s="149">
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="155"/>
+      <c r="K29" s="238"/>
+      <c r="L29" s="239">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M29" s="150">
-        <v>0</v>
-      </c>
-      <c r="N29" s="147">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M29" s="145">
+        <v>0</v>
+      </c>
+      <c r="N29" s="144">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O29" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O29" s="96">
         <f>N29+'prorrateo '!M22</f>
-        <v>342576.70908873709</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="98"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="169" t="s">
+        <v>390569.41908962413</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="97"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="163" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102">
+      <c r="D30" s="101"/>
+      <c r="E30" s="101">
         <v>1.08</v>
       </c>
-      <c r="F30" s="102"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="170"/>
-      <c r="J30" s="171"/>
-      <c r="K30" s="106"/>
-      <c r="L30" s="127">
+      <c r="F30" s="101"/>
+      <c r="G30" s="101"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="165"/>
+      <c r="K30" s="114"/>
+      <c r="L30" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M30" s="107">
-        <v>0</v>
-      </c>
-      <c r="N30" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M30" s="105">
+        <v>0</v>
+      </c>
+      <c r="N30" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O30" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="98"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="169" t="s">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="97"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="102" t="s">
+      <c r="D31" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="102">
+      <c r="E31" s="101">
         <v>1.08</v>
       </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="102"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="171"/>
-      <c r="K31" s="106"/>
-      <c r="L31" s="127">
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="164"/>
+      <c r="J31" s="165"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M31" s="107">
-        <v>0</v>
-      </c>
-      <c r="N31" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M31" s="105">
+        <v>0</v>
+      </c>
+      <c r="N31" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O31" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O31" s="96">
         <f>N31+'prorrateo '!M24</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="99"/>
-      <c r="B32" s="208"/>
-      <c r="C32" s="169" t="s">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="98"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="163" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="102" t="s">
+      <c r="D32" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="102">
+      <c r="E32" s="101">
         <v>1.08</v>
       </c>
-      <c r="F32" s="102"/>
-      <c r="G32" s="102"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="106"/>
-      <c r="L32" s="127">
+      <c r="F32" s="101"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="164"/>
+      <c r="J32" s="165"/>
+      <c r="K32" s="114"/>
+      <c r="L32" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M32" s="107">
-        <v>0</v>
-      </c>
-      <c r="N32" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M32" s="105">
+        <v>0</v>
+      </c>
+      <c r="N32" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O32" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O32" s="96">
         <f>N32+'prorrateo '!M25</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="98"/>
-      <c r="B33" s="90"/>
-      <c r="C33" s="130" t="s">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="97"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="127" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="109" t="s">
+      <c r="D33" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="109">
+      <c r="E33" s="107">
         <v>1.08</v>
       </c>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="110"/>
-      <c r="I33" s="111"/>
-      <c r="J33" s="131"/>
-      <c r="K33" s="113"/>
-      <c r="L33" s="127">
+      <c r="F33" s="107"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="115"/>
+      <c r="L33" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M33" s="107">
-        <v>0</v>
-      </c>
-      <c r="N33" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M33" s="105">
+        <v>0</v>
+      </c>
+      <c r="N33" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O33" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O33" s="96">
         <f>N33+'prorrateo '!M26</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="98"/>
-      <c r="B34" s="90"/>
-      <c r="C34" s="130" t="s">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="97"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="109" t="s">
+      <c r="D34" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="109">
+      <c r="E34" s="107">
         <v>1.08</v>
       </c>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="110"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="131"/>
-      <c r="K34" s="113"/>
-      <c r="L34" s="127">
+      <c r="F34" s="107"/>
+      <c r="G34" s="107"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="109"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="115"/>
+      <c r="L34" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M34" s="107">
-        <v>0</v>
-      </c>
-      <c r="N34" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M34" s="105">
+        <v>0</v>
+      </c>
+      <c r="N34" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O34" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O34" s="96">
         <f>N34+'prorrateo '!M27</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="98">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="97">
         <v>21</v>
       </c>
-      <c r="B35" s="90"/>
-      <c r="C35" s="169" t="s">
+      <c r="B35" s="89"/>
+      <c r="C35" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="102"/>
-      <c r="E35" s="102">
+      <c r="D35" s="101"/>
+      <c r="E35" s="101">
         <v>1.08</v>
       </c>
-      <c r="F35" s="102"/>
-      <c r="G35" s="102"/>
-      <c r="H35" s="104">
-        <v>0</v>
-      </c>
-      <c r="I35" s="170">
+      <c r="F35" s="101"/>
+      <c r="G35" s="101"/>
+      <c r="H35" s="103">
+        <v>0</v>
+      </c>
+      <c r="I35" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="172"/>
-      <c r="K35" s="106"/>
-      <c r="L35" s="127">
+      <c r="J35" s="166"/>
+      <c r="K35" s="114"/>
+      <c r="L35" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M35" s="107">
-        <v>0</v>
-      </c>
-      <c r="N35" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M35" s="105">
+        <v>0</v>
+      </c>
+      <c r="N35" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O35" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O35" s="96">
         <f>N35+'prorrateo '!M28</f>
-        <v>31936.219092719999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="98">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="97">
         <v>22</v>
       </c>
-      <c r="B36" s="90"/>
-      <c r="C36" s="169" t="s">
+      <c r="B36" s="89"/>
+      <c r="C36" s="163" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="102" t="s">
+      <c r="D36" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="102">
+      <c r="E36" s="101">
         <v>1.08</v>
       </c>
-      <c r="F36" s="102"/>
-      <c r="G36" s="102"/>
-      <c r="H36" s="104">
-        <v>0</v>
-      </c>
-      <c r="I36" s="170">
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="103">
+        <v>0</v>
+      </c>
+      <c r="I36" s="164">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="172"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="127">
+      <c r="J36" s="166"/>
+      <c r="K36" s="114"/>
+      <c r="L36" s="235">
         <f t="shared" si="3"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="M36" s="107">
-        <v>0</v>
-      </c>
-      <c r="N36" s="104">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="M36" s="105">
+        <v>0</v>
+      </c>
+      <c r="N36" s="103">
         <f t="shared" si="6"/>
-        <v>3884.8329885600006</v>
-      </c>
-      <c r="O36" s="97">
+        <v>7517.8171969199993</v>
+      </c>
+      <c r="O36" s="96">
         <f>N36+'prorrateo '!M29</f>
-        <v>58550.155246998736</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="98">
+        <v>38329.867945439997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="97">
         <v>23</v>
       </c>
-      <c r="B37" s="90"/>
-      <c r="C37" s="109"/>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="109"/>
-      <c r="G37" s="109"/>
-      <c r="H37" s="110">
-        <v>0</v>
-      </c>
-      <c r="I37" s="111">
+      <c r="B37" s="89"/>
+      <c r="C37" s="107"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="107"/>
+      <c r="H37" s="108">
+        <v>0</v>
+      </c>
+      <c r="I37" s="109">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="132"/>
-      <c r="K37" s="113"/>
-      <c r="L37" s="127">
-        <v>0</v>
-      </c>
-      <c r="M37" s="127">
-        <v>0</v>
-      </c>
-      <c r="N37" s="104">
+      <c r="J37" s="129"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="234">
+        <v>0</v>
+      </c>
+      <c r="M37" s="124">
+        <v>0</v>
+      </c>
+      <c r="N37" s="103">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="98">
+    <row r="38" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="97">
         <v>24</v>
       </c>
-      <c r="B38" s="90"/>
-      <c r="C38" s="109"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="128"/>
-      <c r="F38" s="109"/>
-      <c r="G38" s="109"/>
-      <c r="H38" s="110"/>
-      <c r="I38" s="112"/>
-      <c r="J38" s="117">
+      <c r="B38" s="89"/>
+      <c r="C38" s="107"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="125"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="110"/>
+      <c r="J38" s="115">
         <f>SUM(J10:J37)</f>
-        <v>306814.79180000001</v>
-      </c>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113">
+        <v>322374.05510000011</v>
+      </c>
+      <c r="K38" s="111"/>
+      <c r="L38" s="111">
         <f>SUM(L10:L37)</f>
-        <v>359706.75820000027</v>
-      </c>
-      <c r="M38" s="114"/>
-      <c r="N38" s="110">
+        <v>696094.18490000034</v>
+      </c>
+      <c r="M38" s="112"/>
+      <c r="N38" s="108">
         <f>SUM(N10:N37)</f>
-        <v>666521.54999999958</v>
+        <v>1018468.2400000007</v>
       </c>
       <c r="P38" s="44"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="92"/>
-      <c r="E39" s="134">
+      <c r="C39" s="90"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="131">
         <f>SUM(E10:E38)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="94">
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="93">
         <f>SUM(I10:I38)</f>
-        <v>228.99799999999999</v>
-      </c>
-      <c r="J39" s="126"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="133">
+        <v>240.61100000000013</v>
+      </c>
+      <c r="J39" s="123"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="130">
         <f>L38+J38</f>
-        <v>666521.55000000028</v>
-      </c>
-      <c r="M39" s="93"/>
-      <c r="N39" s="93"/>
+        <v>1018468.2400000005</v>
+      </c>
+      <c r="M39" s="92"/>
+      <c r="N39" s="92"/>
       <c r="O39" s="79"/>
     </row>
-    <row r="40" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="95" t="s">
+    <row r="40" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="234"/>
-      <c r="D40" s="232"/>
-      <c r="E40" s="232"/>
-      <c r="F40" s="232"/>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="95"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C40" s="221"/>
+      <c r="D40" s="219"/>
+      <c r="E40" s="219"/>
+      <c r="F40" s="219"/>
+      <c r="G40" s="219"/>
+      <c r="H40" s="219"/>
+      <c r="I40" s="219"/>
+      <c r="J40" s="219"/>
+      <c r="K40" s="219"/>
+      <c r="L40" s="219"/>
+      <c r="M40" s="219"/>
+      <c r="N40" s="219"/>
+      <c r="O40" s="94"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H41" s="79"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="N41" s="97"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="N41" s="96"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="L44" s="151"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="L45" s="96"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E46" s="152"/>
-      <c r="F46" s="152"/>
-      <c r="G46" s="152"/>
-      <c r="H46" s="152"/>
-      <c r="I46" s="152"/>
-      <c r="J46" s="152"/>
-      <c r="K46" s="152"/>
-      <c r="L46" s="153"/>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L44" s="146"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L45" s="95"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E46" s="147"/>
+      <c r="F46" s="147"/>
+      <c r="G46" s="147"/>
+      <c r="H46" s="147"/>
+      <c r="I46" s="147"/>
+      <c r="J46" s="147"/>
+      <c r="K46" s="147"/>
+      <c r="L46" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/2026/ROSALES/ENERO/expensas rosales Enero.xlsx
+++ b/2026/ROSALES/ENERO/expensas rosales Enero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ROSALES\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6043901-7A20-40AF-86F2-1211428A237F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08354F-2137-4C8C-A979-FF196E963080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="125">
   <si>
     <t>TOTAL</t>
   </si>
@@ -399,7 +399,10 @@
     <t>CUOTA PLAN DE PAGOS (6/6)</t>
   </si>
   <si>
-    <t xml:space="preserve">PREVISION EXTRAORDINARIA </t>
+    <t>Cerrajeria Ayram - copia de llave</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA - ARBA</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1034,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1358,49 +1361,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="171" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="19" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1414,6 +1380,42 @@
     <xf numFmtId="171" fontId="28" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="28" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="33" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="11" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1502,12 +1504,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2457450" cy="981076"/>
+    <xdr:ext cx="1647825" cy="981076"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="image1.jpg">
@@ -1527,8 +1529,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6496050" y="409575"/>
-          <a:ext cx="2457450" cy="981076"/>
+          <a:off x="1581150" y="371475"/>
+          <a:ext cx="1647825" cy="981076"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1831,7 +1833,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F65"/>
+  <dimension ref="A2:F66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2052,59 +2054,64 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B30" s="42"/>
       <c r="C30" s="33">
-        <v>55000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="D30" s="45"/>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="33">
+        <v>55000</v>
+      </c>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="40"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="23">
-        <f>SUM(C25:C31)</f>
-        <v>516751.05699999997</v>
-      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="6"/>
       <c r="F32" s="12"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="40"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="23">
+        <f>SUM(C25:C32)</f>
+        <v>528751.05700000003</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="43">
-        <f>+C32+C24</f>
-        <v>2156873.477</v>
-      </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C34" s="24"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="43">
+        <f>+C33+C24</f>
+        <v>2168873.477</v>
+      </c>
       <c r="F34" s="12"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="C35" s="24"/>
       <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="202"/>
+      <c r="A36" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="24"/>
       <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -2116,204 +2123,210 @@
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
+      <c r="C38" s="202"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C39" s="25"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="34"/>
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="167" t="s">
-        <v>123</v>
-      </c>
-      <c r="B40" s="167"/>
-      <c r="C40" s="168">
-        <v>0</v>
-      </c>
+      <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C41" s="25"/>
+      <c r="A41" s="167" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="167"/>
+      <c r="C41" s="168">
+        <v>1500000</v>
+      </c>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C42" s="25"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14">
-        <f>+C36+C37+C38+C41</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="14">
+        <f>+C37+C38+C39+C42</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19">
-        <f>+C42+C33</f>
-        <v>2156873.477</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="C46" s="149"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="192" t="s">
-        <v>99</v>
-      </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="193">
-        <v>39116.323591710112</v>
-      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="19">
+        <f>+C43+C34</f>
+        <v>2168873.477</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="C47" s="149"/>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="192" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B48" s="28"/>
-      <c r="C48" s="207">
-        <f>-(C44-C31)</f>
-        <v>-2156873.477</v>
+      <c r="C48" s="193">
+        <v>39116.323591710112</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="192" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="207">
+        <f>-(C45-C32)</f>
+        <v>-2168873.477</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="192" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="194">
+      <c r="B50" s="28"/>
+      <c r="C50" s="194">
         <f>'prorrateo '!F31</f>
         <v>2899814.6830321611</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="192" t="s">
-        <v>113</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="206">
-        <v>-1018468.24</v>
-      </c>
-    </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="192" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B51" s="28"/>
-      <c r="C51" s="31">
-        <v>0</v>
+      <c r="C51" s="206">
+        <v>-1018468.24</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="192" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B52" s="28"/>
-      <c r="C52" s="231">
-        <v>107386.2</v>
+      <c r="C52" s="31">
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="192" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="216">
+        <v>107386.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="192" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="193">
-        <f>SUM(C47:C52)</f>
-        <v>-129024.51037612879</v>
-      </c>
-      <c r="D53" s="5"/>
-    </row>
-    <row r="54" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="210"/>
-      <c r="B55" s="210"/>
-      <c r="C55" s="210"/>
-      <c r="F55" s="44"/>
-    </row>
-    <row r="56" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="211"/>
-      <c r="B56" s="211"/>
-      <c r="C56" s="211"/>
-    </row>
-    <row r="57" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="26" t="s">
+      <c r="B54" s="28"/>
+      <c r="C54" s="193">
+        <f>SUM(C48:C53)</f>
+        <v>-141024.51037612878</v>
+      </c>
+      <c r="D54" s="5"/>
+    </row>
+    <row r="55" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="10"/>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="225"/>
+      <c r="B56" s="225"/>
+      <c r="C56" s="225"/>
+      <c r="F56" s="44"/>
+    </row>
+    <row r="57" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="226"/>
+      <c r="B57" s="226"/>
+      <c r="C57" s="226"/>
+    </row>
+    <row r="58" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
+      <c r="B58" s="27"/>
+      <c r="C58" s="29"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="31">
-        <f>-C42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="28"/>
       <c r="B59" s="28"/>
-      <c r="C59" s="31"/>
+      <c r="C59" s="31">
+        <f>-C43</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="28"/>
       <c r="B60" s="28"/>
-      <c r="C60" s="32"/>
+      <c r="C60" s="31"/>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="150" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="151"/>
-      <c r="C61" s="152">
-        <f>SUM(C57:C60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="212" t="s">
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="32"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="151"/>
+      <c r="C62" s="152">
+        <f>SUM(C58:C61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="227" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="213"/>
-      <c r="C62" s="213"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="213"/>
-      <c r="B63" s="213"/>
-      <c r="C63" s="213"/>
-    </row>
-    <row r="64" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="213"/>
-      <c r="B64" s="213"/>
-      <c r="C64" s="213"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+      <c r="B63" s="228"/>
+      <c r="C63" s="228"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="228"/>
+      <c r="B64" s="228"/>
+      <c r="C64" s="228"/>
+    </row>
+    <row r="65" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="228"/>
+      <c r="B65" s="228"/>
+      <c r="C65" s="228"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A55:C56"/>
-    <mergeCell ref="A62:C64"/>
+    <mergeCell ref="A56:C57"/>
+    <mergeCell ref="A63:C65"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2321,7 +2334,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="87" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2355,30 +2368,30 @@
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="214">
+      <c r="B1" s="229">
         <f>N1</f>
-        <v>2156873.477</v>
-      </c>
-      <c r="C1" s="214"/>
+        <v>2168873.477</v>
+      </c>
+      <c r="C1" s="229"/>
       <c r="D1" s="135">
         <v>1667839.1270000001</v>
       </c>
       <c r="E1" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="217" t="s">
+      <c r="G1" s="231"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="214">
-        <v>0</v>
-      </c>
-      <c r="M1" s="214"/>
+      <c r="J1" s="232"/>
+      <c r="K1" s="232"/>
+      <c r="L1" s="229">
+        <v>1500000</v>
+      </c>
+      <c r="M1" s="229"/>
       <c r="N1">
-        <v>2156873.477</v>
+        <v>2168873.477</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2441,11 +2454,11 @@
       <c r="E3" s="126">
         <v>153001.36328172</v>
       </c>
-      <c r="F3" s="225">
+      <c r="F3" s="204">
         <f>E3</f>
         <v>153001.36328172</v>
       </c>
-      <c r="G3" s="226">
+      <c r="G3" s="212">
         <f>E3-F3</f>
         <v>0</v>
       </c>
@@ -2455,7 +2468,7 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>110216.2346747</v>
+        <v>110829.43467469999</v>
       </c>
       <c r="J3" s="56">
         <f>Edesur!N10</f>
@@ -2467,16 +2480,16 @@
       </c>
       <c r="L3" s="56">
         <f>L$1*D3/100</f>
-        <v>0</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="M3" s="57">
         <f>I3+G3+L3+K3+H3+J3</f>
-        <v>167882.86472309002</v>
+        <v>245146.06472309006</v>
       </c>
       <c r="N3" s="44"/>
       <c r="O3" s="146">
         <f>M3-J3</f>
-        <v>110216.23467469998</v>
+        <v>187479.43467470002</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -2495,11 +2508,11 @@
       <c r="E4" s="126">
         <v>148167.69116867997</v>
       </c>
-      <c r="F4" s="225">
+      <c r="F4" s="204">
         <f>E4</f>
         <v>148167.69116867997</v>
       </c>
-      <c r="G4" s="226">
+      <c r="G4" s="212">
         <f t="shared" ref="G4:G29" si="0">E4-F4</f>
         <v>0</v>
       </c>
@@ -2509,7 +2522,7 @@
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="2">B$1*D4/100</f>
-        <v>109784.8599793</v>
+        <v>110395.65997929999</v>
       </c>
       <c r="J4" s="56">
         <f>Edesur!N11</f>
@@ -2521,16 +2534,16 @@
       </c>
       <c r="L4" s="56">
         <f t="shared" ref="L4:L29" si="4">L$1*D4/100</f>
-        <v>0</v>
+        <v>76350</v>
       </c>
       <c r="M4" s="57">
         <f t="shared" ref="M4:M29" si="5">I4+G4+L4+K4+H4+J4</f>
-        <v>160765.93859071002</v>
+        <v>237726.73859071001</v>
       </c>
       <c r="N4" s="44"/>
       <c r="O4" s="146">
         <f t="shared" ref="O4:O29" si="6">M4-J4</f>
-        <v>109784.8599793</v>
+        <v>186745.65997929999</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2547,11 +2560,11 @@
       <c r="E5" s="126">
         <v>187753.45675376873</v>
       </c>
-      <c r="F5" s="225">
+      <c r="F5" s="204">
         <f>215804.85-F23</f>
         <v>187753.46389584002</v>
       </c>
-      <c r="G5" s="226">
+      <c r="G5" s="212">
         <f t="shared" si="0"/>
         <v>-7.1420712920371443E-3</v>
       </c>
@@ -2561,7 +2574,7 @@
       </c>
       <c r="I5" s="56">
         <f t="shared" si="2"/>
-        <v>108706.4232408</v>
+        <v>109311.2232408</v>
       </c>
       <c r="J5" s="56">
         <f>Edesur!N12</f>
@@ -2573,16 +2586,16 @@
       </c>
       <c r="L5" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="M5" s="57">
         <f t="shared" si="5"/>
-        <v>178593.91871768871</v>
+        <v>254798.71871768872</v>
       </c>
       <c r="N5" s="44"/>
       <c r="O5" s="146">
         <f t="shared" si="6"/>
-        <v>108706.41609872869</v>
+        <v>184911.21609872871</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2600,7 +2613,7 @@
         <v>151256.37574692001</v>
       </c>
       <c r="F6" s="204"/>
-      <c r="G6" s="227">
+      <c r="G6" s="213">
         <f t="shared" si="0"/>
         <v>151256.37574692001</v>
       </c>
@@ -2610,7 +2623,7 @@
       </c>
       <c r="I6" s="64">
         <f t="shared" si="2"/>
-        <v>112373.1081517</v>
+        <v>112998.3081517</v>
       </c>
       <c r="J6" s="64">
         <f>Edesur!N13</f>
@@ -2622,15 +2635,15 @@
       </c>
       <c r="L6" s="64">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>78150</v>
       </c>
       <c r="M6" s="203">
         <f t="shared" si="5"/>
-        <v>311432.78546178679</v>
+        <v>390207.9854617868</v>
       </c>
       <c r="O6" s="146">
         <f t="shared" si="6"/>
-        <v>269679.73892849678</v>
+        <v>348454.93892849679</v>
       </c>
       <c r="P6" s="169"/>
     </row>
@@ -2650,11 +2663,11 @@
       <c r="E7" s="126">
         <v>152954.46978172002</v>
       </c>
-      <c r="F7" s="225">
+      <c r="F7" s="204">
         <f>181005.86-F28</f>
         <v>152954.47389584</v>
       </c>
-      <c r="G7" s="226">
+      <c r="G7" s="212">
         <f t="shared" si="0"/>
         <v>-4.1141199762932956E-3</v>
       </c>
@@ -2664,7 +2677,7 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="2"/>
-        <v>110216.2346747</v>
+        <v>110829.43467469999</v>
       </c>
       <c r="J7" s="56">
         <f>Edesur!N14</f>
@@ -2676,15 +2689,15 @@
       </c>
       <c r="L7" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="M7" s="57">
         <f t="shared" si="5"/>
-        <v>167695.28660897003</v>
+        <v>244958.48660897004</v>
       </c>
       <c r="O7" s="146">
         <f t="shared" si="6"/>
-        <v>110216.23056058004</v>
+        <v>187479.43056058005</v>
       </c>
       <c r="P7" s="169"/>
     </row>
@@ -2702,11 +2715,11 @@
       <c r="E8" s="126">
         <v>153579.20106868001</v>
       </c>
-      <c r="F8" s="225">
-        <f t="shared" ref="F7:F11" si="7">E8</f>
+      <c r="F8" s="204">
+        <f t="shared" ref="F8:F10" si="7">E8</f>
         <v>153579.20106868001</v>
       </c>
-      <c r="G8" s="226">
+      <c r="G8" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2716,7 +2729,7 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="2"/>
-        <v>109784.8599793</v>
+        <v>110395.65997929999</v>
       </c>
       <c r="J8" s="56">
         <f>Edesur!N15</f>
@@ -2728,15 +2741,15 @@
       </c>
       <c r="L8" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76350</v>
       </c>
       <c r="M8" s="57">
         <f t="shared" si="5"/>
-        <v>167490.46649070998</v>
+        <v>244451.26649070997</v>
       </c>
       <c r="O8" s="146">
         <f t="shared" si="6"/>
-        <v>109784.85997929999</v>
+        <v>186745.65997929999</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2753,11 +2766,11 @@
       <c r="E9" s="126">
         <v>145197.56902720104</v>
       </c>
-      <c r="F9" s="225">
+      <c r="F9" s="204">
         <f>E9</f>
         <v>145197.56902720104</v>
       </c>
-      <c r="G9" s="226">
+      <c r="G9" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2767,7 +2780,7 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="2"/>
-        <v>110216.2346747</v>
+        <v>110829.43467469999</v>
       </c>
       <c r="J9" s="56">
         <f>Edesur!N16</f>
@@ -2779,15 +2792,15 @@
       </c>
       <c r="L9" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="M9" s="57">
         <f t="shared" si="5"/>
-        <v>154433.80892308999</v>
+        <v>231697.00892309</v>
       </c>
       <c r="O9" s="146">
         <f t="shared" si="6"/>
-        <v>110216.23467470001</v>
+        <v>187479.43467470002</v>
       </c>
       <c r="P9" s="169"/>
     </row>
@@ -2807,18 +2820,18 @@
       <c r="E10" s="175">
         <v>135028.13246867998</v>
       </c>
-      <c r="F10" s="230">
+      <c r="F10" s="238">
         <f t="shared" si="7"/>
         <v>135028.13246867998</v>
       </c>
-      <c r="G10" s="228">
+      <c r="G10" s="214">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H10" s="176"/>
       <c r="I10" s="176">
         <f t="shared" si="2"/>
-        <v>109784.8599793</v>
+        <v>110395.65997929999</v>
       </c>
       <c r="J10" s="176">
         <f>Edesur!N17</f>
@@ -2830,15 +2843,15 @@
       </c>
       <c r="L10" s="176">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76350</v>
       </c>
       <c r="M10" s="177">
         <f t="shared" si="5"/>
-        <v>147964.01309071001</v>
+        <v>224924.81309071</v>
       </c>
       <c r="O10" s="146">
         <f t="shared" si="6"/>
-        <v>109784.8599793</v>
+        <v>186745.65997929999</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2856,7 +2869,7 @@
         <v>143136.29328608001</v>
       </c>
       <c r="F11" s="204"/>
-      <c r="G11" s="226">
+      <c r="G11" s="212">
         <f t="shared" si="0"/>
         <v>143136.29328608001</v>
       </c>
@@ -2866,7 +2879,7 @@
       </c>
       <c r="I11" s="56">
         <f t="shared" si="2"/>
-        <v>108706.4232408</v>
+        <v>109311.2232408</v>
       </c>
       <c r="J11" s="56">
         <f>Edesur!N18</f>
@@ -2878,15 +2891,15 @@
       </c>
       <c r="L11" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="M11" s="57">
         <f t="shared" si="5"/>
-        <v>303605.63677728322</v>
+        <v>379810.43677728315</v>
       </c>
       <c r="O11" s="146">
         <f t="shared" si="6"/>
-        <v>257568.16825832322</v>
+        <v>333772.96825832315</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2903,11 +2916,11 @@
       <c r="E12" s="126">
         <v>167106.37874692006</v>
       </c>
-      <c r="F12" s="225">
+      <c r="F12" s="204">
         <f t="shared" ref="F12" si="8">E12</f>
         <v>167106.37874692006</v>
       </c>
-      <c r="G12" s="226">
+      <c r="G12" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2917,7 +2930,7 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="2"/>
-        <v>112373.1081517</v>
+        <v>112998.3081517</v>
       </c>
       <c r="J12" s="56">
         <f>Edesur!N19</f>
@@ -2929,15 +2942,15 @@
       </c>
       <c r="L12" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>78150</v>
       </c>
       <c r="M12" s="57">
         <f t="shared" si="5"/>
-        <v>174637.37158498997</v>
+        <v>253412.57158498999</v>
       </c>
       <c r="O12" s="146">
         <f t="shared" si="6"/>
-        <v>112373.1081517</v>
+        <v>191148.30815170001</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2956,11 +2969,11 @@
       <c r="E13" s="126">
         <v>162201.86798172005</v>
       </c>
-      <c r="F13" s="225">
+      <c r="F13" s="204">
         <f>190253.26-F24</f>
         <v>162201.87389584002</v>
       </c>
-      <c r="G13" s="226">
+      <c r="G13" s="212">
         <f t="shared" si="0"/>
         <v>-5.9141199744772166E-3</v>
       </c>
@@ -2970,7 +2983,7 @@
       </c>
       <c r="I13" s="56">
         <f t="shared" si="2"/>
-        <v>110216.2346747</v>
+        <v>110829.43467469999</v>
       </c>
       <c r="J13" s="56">
         <f>Edesur!N20</f>
@@ -2982,16 +2995,16 @@
       </c>
       <c r="L13" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76650.000000000015</v>
       </c>
       <c r="M13" s="57">
         <f t="shared" si="5"/>
-        <v>176361.20360897004</v>
+        <v>253624.40360897002</v>
       </c>
       <c r="N13" s="44"/>
       <c r="O13" s="146">
         <f t="shared" si="6"/>
-        <v>110216.22876058004</v>
+        <v>187479.42876058002</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -3010,11 +3023,11 @@
       <c r="E14" s="126">
         <v>138995.71226398699</v>
       </c>
-      <c r="F14" s="225">
+      <c r="F14" s="204">
         <f>167047.02-F25</f>
         <v>138995.63389584</v>
       </c>
-      <c r="G14" s="227">
+      <c r="G14" s="213">
         <f t="shared" si="0"/>
         <v>7.8368146991124377E-2</v>
       </c>
@@ -3024,7 +3037,7 @@
       </c>
       <c r="I14" s="64">
         <f t="shared" si="2"/>
-        <v>109784.8599793</v>
+        <v>110395.65997929999</v>
       </c>
       <c r="J14" s="56">
         <f>Edesur!N21</f>
@@ -3036,15 +3049,15 @@
       </c>
       <c r="L14" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>76350</v>
       </c>
       <c r="M14" s="57">
         <f t="shared" si="5"/>
-        <v>151452.97099358286</v>
+        <v>228413.77099358285</v>
       </c>
       <c r="O14" s="146">
         <f t="shared" si="6"/>
-        <v>109784.94148217287</v>
+        <v>186745.74148217286</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -3063,11 +3076,11 @@
       <c r="E15" s="126">
         <v>279407.3046097632</v>
       </c>
-      <c r="F15" s="225">
+      <c r="F15" s="204">
         <f>334072.62-F29</f>
         <v>279407.29774156125</v>
       </c>
-      <c r="G15" s="226">
+      <c r="G15" s="212">
         <f t="shared" si="0"/>
         <v>6.8682019482366741E-3</v>
       </c>
@@ -3077,7 +3090,7 @@
       </c>
       <c r="I15" s="56">
         <f t="shared" si="2"/>
-        <v>108706.4232408</v>
+        <v>109311.2232408</v>
       </c>
       <c r="J15" s="56">
         <f>Edesur!N22</f>
@@ -3089,15 +3102,15 @@
       </c>
       <c r="L15" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="M15" s="57">
         <f t="shared" si="5"/>
-        <v>153093.24770269002</v>
+        <v>229298.04770269</v>
       </c>
       <c r="O15" s="146">
         <f t="shared" si="6"/>
-        <v>108706.43038373004</v>
+        <v>184911.23038373003</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -3116,11 +3129,11 @@
       <c r="E16" s="126">
         <v>159322.05774691998</v>
       </c>
-      <c r="F16" s="225">
+      <c r="F16" s="204">
         <f>187373.45-F21</f>
         <v>159322.06389584002</v>
       </c>
-      <c r="G16" s="226">
+      <c r="G16" s="212">
         <f t="shared" si="0"/>
         <v>-6.1489200452342629E-3</v>
       </c>
@@ -3130,7 +3143,7 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="2"/>
-        <v>112373.1081517</v>
+        <v>112998.3081517</v>
       </c>
       <c r="J16" s="56">
         <f>Edesur!N23</f>
@@ -3142,16 +3155,16 @@
       </c>
       <c r="L16" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>78150</v>
       </c>
       <c r="M16" s="57">
         <f t="shared" si="5"/>
-        <v>178707.72123606998</v>
+        <v>257482.92123606999</v>
       </c>
       <c r="N16" s="44"/>
       <c r="O16" s="146">
         <f t="shared" si="6"/>
-        <v>112373.10200277995</v>
+        <v>191148.30200277996</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -3168,11 +3181,11 @@
       <c r="E17" s="126">
         <v>135108.12608607998</v>
       </c>
-      <c r="F17" s="225">
+      <c r="F17" s="204">
         <f>E17+134891.87</f>
         <v>269999.99608607998</v>
       </c>
-      <c r="G17" s="226">
+      <c r="G17" s="212">
         <f t="shared" si="0"/>
         <v>-134891.87</v>
       </c>
@@ -3182,7 +3195,7 @@
       </c>
       <c r="I17" s="56">
         <f t="shared" si="2"/>
-        <v>108706.4232408</v>
+        <v>109311.2232408</v>
       </c>
       <c r="J17" s="56">
         <f>Edesur!N24</f>
@@ -3194,15 +3207,15 @@
       </c>
       <c r="L17" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>75600</v>
       </c>
       <c r="M17" s="57">
         <f t="shared" si="5"/>
-        <v>21596.459959760003</v>
+        <v>97801.259959760006</v>
       </c>
       <c r="O17" s="146">
         <f t="shared" si="6"/>
-        <v>-26185.4467592</v>
+        <v>50019.353240800003</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3219,11 +3232,11 @@
       <c r="E18" s="126">
         <v>142824.92444691999</v>
       </c>
-      <c r="F18" s="225">
-        <f t="shared" ref="F16:F21" si="9">E18</f>
+      <c r="F18" s="204">
+        <f t="shared" ref="F18:F21" si="9">E18</f>
         <v>142824.92444691999</v>
       </c>
-      <c r="G18" s="227">
+      <c r="G18" s="213">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3233,7 +3246,7 @@
       </c>
       <c r="I18" s="64">
         <f t="shared" si="2"/>
-        <v>112373.1081517</v>
+        <v>112998.3081517</v>
       </c>
       <c r="J18" s="56">
         <f>Edesur!N25</f>
@@ -3245,16 +3258,16 @@
       </c>
       <c r="L18" s="64">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>78150</v>
       </c>
       <c r="M18" s="57">
         <f t="shared" si="5"/>
-        <v>160494.29198499001</v>
+        <v>239269.49198499002</v>
       </c>
       <c r="N18" s="199"/>
       <c r="O18" s="146">
         <f t="shared" si="6"/>
-        <v>112373.1081517</v>
+        <v>191148.30815170001</v>
       </c>
       <c r="P18" s="198"/>
       <c r="Q18" s="195"/>
@@ -3273,11 +3286,11 @@
       <c r="E19" s="126">
         <v>225198.20842479993</v>
       </c>
-      <c r="F19" s="225">
+      <c r="F19" s="204">
         <f t="shared" si="9"/>
         <v>225198.20842479993</v>
       </c>
-      <c r="G19" s="227">
+      <c r="G19" s="213">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3287,7 +3300,7 @@
       </c>
       <c r="I19" s="64">
         <f t="shared" si="2"/>
-        <v>159608.63729800002</v>
+        <v>160496.63729800002</v>
       </c>
       <c r="J19" s="56">
         <f>Edesur!N26</f>
@@ -3299,15 +3312,15 @@
       </c>
       <c r="L19" s="64">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="M19" s="57">
         <f t="shared" si="5"/>
-        <v>262289.79418060003</v>
+        <v>374177.79418060009</v>
       </c>
       <c r="O19" s="146">
         <f t="shared" si="6"/>
-        <v>159608.63729799999</v>
+        <v>271496.63729800005</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="24" x14ac:dyDescent="0.25">
@@ -3324,18 +3337,18 @@
       <c r="E20" s="175">
         <v>28051.386104159999</v>
       </c>
-      <c r="F20" s="230">
+      <c r="F20" s="238">
         <f t="shared" si="9"/>
         <v>28051.386104159999</v>
       </c>
-      <c r="G20" s="228">
+      <c r="G20" s="214">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H20" s="176"/>
       <c r="I20" s="176">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J20" s="176">
         <f>Edesur!N27</f>
@@ -3347,15 +3360,15 @@
       </c>
       <c r="L20" s="176">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M20" s="177">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O20" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -3372,11 +3385,11 @@
       <c r="E21" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F21" s="225">
+      <c r="F21" s="204">
         <f t="shared" si="9"/>
         <v>28051.386104159999</v>
       </c>
-      <c r="G21" s="226">
+      <c r="G21" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3386,7 +3399,7 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J21" s="56">
         <f>Edesur!N28</f>
@@ -3398,15 +3411,15 @@
       </c>
       <c r="L21" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M21" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O21" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -3424,7 +3437,7 @@
       <c r="F22" s="205">
         <v>0</v>
       </c>
-      <c r="G22" s="229">
+      <c r="G22" s="215">
         <f t="shared" si="0"/>
         <v>338691.87610017706</v>
       </c>
@@ -3434,7 +3447,7 @@
       </c>
       <c r="I22" s="141">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J22" s="141">
         <f>Edesur!N29</f>
@@ -3446,15 +3459,15 @@
       </c>
       <c r="L22" s="141">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M22" s="142">
         <f t="shared" si="5"/>
-        <v>383051.60189270414</v>
+        <v>399381.20189270412</v>
       </c>
       <c r="O22" s="146">
         <f t="shared" si="6"/>
-        <v>375533.78469578415</v>
+        <v>391863.38469578413</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -3471,11 +3484,11 @@
       <c r="E23" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F23" s="225">
+      <c r="F23" s="204">
         <f>E23</f>
         <v>28051.386104159999</v>
       </c>
-      <c r="G23" s="226">
+      <c r="G23" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3485,7 +3498,7 @@
       </c>
       <c r="I23" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J23" s="56">
         <f>Edesur!N30</f>
@@ -3497,15 +3510,15 @@
       </c>
       <c r="L23" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M23" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O23" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -3524,11 +3537,11 @@
       <c r="E24" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F24" s="225">
+      <c r="F24" s="204">
         <f t="shared" ref="F24" si="10">E24</f>
         <v>28051.386104159999</v>
       </c>
-      <c r="G24" s="226">
+      <c r="G24" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3538,7 +3551,7 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J24" s="56">
         <f>Edesur!N31</f>
@@ -3550,15 +3563,15 @@
       </c>
       <c r="L24" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M24" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O24" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -3577,11 +3590,11 @@
       <c r="E25" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F25" s="225">
+      <c r="F25" s="204">
         <f>E25</f>
         <v>28051.386104159999</v>
       </c>
-      <c r="G25" s="226">
+      <c r="G25" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3591,7 +3604,7 @@
       </c>
       <c r="I25" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J25" s="56">
         <f>Edesur!N32</f>
@@ -3603,15 +3616,15 @@
       </c>
       <c r="L25" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M25" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O25" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -3628,11 +3641,11 @@
       <c r="E26" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F26" s="225">
+      <c r="F26" s="204">
         <f t="shared" ref="F26:F28" si="11">E26</f>
         <v>28051.386104159999</v>
       </c>
-      <c r="G26" s="226">
+      <c r="G26" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3642,7 +3655,7 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J26" s="56">
         <f>Edesur!N33</f>
@@ -3654,15 +3667,15 @@
       </c>
       <c r="L26" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M26" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O26" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -3679,11 +3692,11 @@
       <c r="E27" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F27" s="225">
+      <c r="F27" s="204">
         <f t="shared" si="11"/>
         <v>28051.386104159999</v>
       </c>
-      <c r="G27" s="226">
+      <c r="G27" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3693,7 +3706,7 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J27" s="56">
         <f>Edesur!N34</f>
@@ -3705,15 +3718,15 @@
       </c>
       <c r="L27" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M27" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O27" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
       <c r="P27" s="44">
         <f>F27+F26+F19</f>
@@ -3735,11 +3748,11 @@
       <c r="E28" s="126">
         <v>28051.386104159999</v>
       </c>
-      <c r="F28" s="225">
+      <c r="F28" s="204">
         <f t="shared" si="11"/>
         <v>28051.386104159999</v>
       </c>
-      <c r="G28" s="226">
+      <c r="G28" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3749,7 +3762,7 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J28" s="56">
         <f>Edesur!N35</f>
@@ -3761,15 +3774,15 @@
       </c>
       <c r="L28" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M28" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O28" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -3788,11 +3801,11 @@
       <c r="E29" s="126">
         <v>54665.322258438733</v>
       </c>
-      <c r="F29" s="225">
+      <c r="F29" s="204">
         <f>E29</f>
         <v>54665.322258438733</v>
       </c>
-      <c r="G29" s="226">
+      <c r="G29" s="212">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3802,7 +3815,7 @@
       </c>
       <c r="I29" s="56">
         <f t="shared" si="2"/>
-        <v>23294.233551600002</v>
+        <v>23423.833551600004</v>
       </c>
       <c r="J29" s="56">
         <f>Edesur!N36</f>
@@ -3814,15 +3827,15 @@
       </c>
       <c r="L29" s="56">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M29" s="57">
         <f t="shared" si="5"/>
-        <v>30812.05074852</v>
+        <v>47141.650748520005</v>
       </c>
       <c r="O29" s="146">
         <f t="shared" si="6"/>
-        <v>23294.233551600002</v>
+        <v>39623.833551600008</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -3859,7 +3872,7 @@
       <c r="H31" s="75"/>
       <c r="I31" s="133">
         <f>SUM(I3:I30)</f>
-        <v>2156873.477</v>
+        <v>2168873.4770000014</v>
       </c>
       <c r="J31" s="133"/>
       <c r="K31" s="133">
@@ -3869,73 +3882,73 @@
       <c r="L31" s="132"/>
       <c r="M31" s="132">
         <f>SUM(M3:M29)</f>
-        <v>3698857.839265076</v>
+        <v>5210857.8392650764</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="K32" s="22"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="215" t="s">
+      <c r="A33" s="230" t="s">
         <v>108</v>
       </c>
-      <c r="B33" s="215"/>
-      <c r="C33" s="215"/>
-      <c r="D33" s="215"/>
-      <c r="E33" s="215"/>
-      <c r="F33" s="215"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="215"/>
-      <c r="I33" s="215"/>
-      <c r="J33" s="215"/>
-      <c r="K33" s="215"/>
-      <c r="L33" s="215"/>
-      <c r="M33" s="215"/>
+      <c r="B33" s="230"/>
+      <c r="C33" s="230"/>
+      <c r="D33" s="230"/>
+      <c r="E33" s="230"/>
+      <c r="F33" s="230"/>
+      <c r="G33" s="230"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="230"/>
+      <c r="J33" s="230"/>
+      <c r="K33" s="230"/>
+      <c r="L33" s="230"/>
+      <c r="M33" s="230"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="215"/>
-      <c r="B34" s="215"/>
-      <c r="C34" s="215"/>
-      <c r="D34" s="215"/>
-      <c r="E34" s="215"/>
-      <c r="F34" s="215"/>
-      <c r="G34" s="215"/>
-      <c r="H34" s="215"/>
-      <c r="I34" s="215"/>
-      <c r="J34" s="215"/>
-      <c r="K34" s="215"/>
-      <c r="L34" s="215"/>
-      <c r="M34" s="215"/>
+      <c r="A34" s="230"/>
+      <c r="B34" s="230"/>
+      <c r="C34" s="230"/>
+      <c r="D34" s="230"/>
+      <c r="E34" s="230"/>
+      <c r="F34" s="230"/>
+      <c r="G34" s="230"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="230"/>
+      <c r="J34" s="230"/>
+      <c r="K34" s="230"/>
+      <c r="L34" s="230"/>
+      <c r="M34" s="230"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="215"/>
-      <c r="B35" s="215"/>
-      <c r="C35" s="215"/>
-      <c r="D35" s="215"/>
-      <c r="E35" s="215"/>
-      <c r="F35" s="215"/>
-      <c r="G35" s="215"/>
-      <c r="H35" s="215"/>
-      <c r="I35" s="215"/>
-      <c r="J35" s="215"/>
-      <c r="K35" s="215"/>
-      <c r="L35" s="215"/>
-      <c r="M35" s="215"/>
+      <c r="A35" s="230"/>
+      <c r="B35" s="230"/>
+      <c r="C35" s="230"/>
+      <c r="D35" s="230"/>
+      <c r="E35" s="230"/>
+      <c r="F35" s="230"/>
+      <c r="G35" s="230"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="230"/>
+      <c r="J35" s="230"/>
+      <c r="K35" s="230"/>
+      <c r="L35" s="230"/>
+      <c r="M35" s="230"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="215"/>
-      <c r="B36" s="215"/>
-      <c r="C36" s="215"/>
-      <c r="D36" s="215"/>
-      <c r="E36" s="215"/>
-      <c r="F36" s="215"/>
-      <c r="G36" s="215"/>
-      <c r="H36" s="215"/>
-      <c r="I36" s="215"/>
-      <c r="J36" s="215"/>
-      <c r="K36" s="215"/>
-      <c r="L36" s="215"/>
-      <c r="M36" s="215"/>
+      <c r="A36" s="230"/>
+      <c r="B36" s="230"/>
+      <c r="C36" s="230"/>
+      <c r="D36" s="230"/>
+      <c r="E36" s="230"/>
+      <c r="F36" s="230"/>
+      <c r="G36" s="230"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="230"/>
+      <c r="J36" s="230"/>
+      <c r="K36" s="230"/>
+      <c r="L36" s="230"/>
+      <c r="M36" s="230"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3962,37 +3975,37 @@
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.85546875" customWidth="1"/>
     <col min="15" max="15" width="11.42578125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="233" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
+      <c r="L1" s="234"/>
+      <c r="M1" s="234"/>
+      <c r="N1" s="235"/>
       <c r="O1" s="76"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -4095,8 +4108,8 @@
       <c r="B7" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="224">
-        <f>-'detalle y gastos'!C50</f>
+      <c r="C7" s="211">
+        <f>-'detalle y gastos'!C51</f>
         <v>1018468.24</v>
       </c>
       <c r="D7" s="28"/>
@@ -4125,15 +4138,15 @@
       <c r="H8" s="83"/>
       <c r="I8" s="82"/>
       <c r="J8" s="78"/>
-      <c r="K8" s="222">
+      <c r="K8" s="210">
         <f>C8-J38</f>
         <v>-322374.05510000011</v>
       </c>
-      <c r="L8" s="223">
+      <c r="L8" s="237">
         <f>C7-J38</f>
         <v>696094.18489999988</v>
       </c>
-      <c r="M8" s="223"/>
+      <c r="M8" s="237"/>
       <c r="N8" s="84"/>
       <c r="O8" s="78"/>
       <c r="P8" s="11"/>
@@ -4169,10 +4182,10 @@
       <c r="J9" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="232" t="s">
+      <c r="K9" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="232" t="s">
+      <c r="L9" s="217" t="s">
         <v>84</v>
       </c>
       <c r="M9" s="122" t="s">
@@ -4221,7 +4234,7 @@
         <f>K8*E10%</f>
         <v>-16473.314215610008</v>
       </c>
-      <c r="L10" s="235">
+      <c r="L10" s="220">
         <f>L$8*E10/S$12</f>
         <v>35570.412848389999</v>
       </c>
@@ -4235,7 +4248,7 @@
       </c>
       <c r="O10" s="96">
         <f>N10+'prorrateo '!M3</f>
-        <v>225549.49477148007</v>
+        <v>302812.69477148011</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -4277,7 +4290,7 @@
         <f>K8*E11%</f>
         <v>-16408.839404590006</v>
       </c>
-      <c r="L11" s="235">
+      <c r="L11" s="220">
         <f t="shared" ref="L11:L36" si="3">L$8*E11/S$12</f>
         <v>35431.194011409993</v>
       </c>
@@ -4291,7 +4304,7 @@
       </c>
       <c r="O11" s="96">
         <f>N11+'prorrateo '!M4</f>
-        <v>211747.01720212004</v>
+        <v>288707.81720212003</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4333,7 +4346,7 @@
         <f>K8*E12%</f>
         <v>-16247.652377040005</v>
       </c>
-      <c r="L12" s="235">
+      <c r="L12" s="220">
         <f t="shared" si="3"/>
         <v>35083.146918959996</v>
       </c>
@@ -4347,7 +4360,7 @@
       </c>
       <c r="O12" s="96">
         <f>N12+'prorrateo '!M5</f>
-        <v>248481.42133664872</v>
+        <v>324686.22133664874</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4388,11 +4401,11 @@
         <f t="shared" si="2"/>
         <v>5486.5395000000008</v>
       </c>
-      <c r="K13" s="236">
+      <c r="K13" s="221">
         <f>K8*E13%</f>
         <v>-16795.688270710005</v>
       </c>
-      <c r="L13" s="235">
+      <c r="L13" s="220">
         <f t="shared" si="3"/>
         <v>36266.507033289992</v>
       </c>
@@ -4406,7 +4419,7 @@
       </c>
       <c r="O13" s="96">
         <f>N13+'prorrateo '!M6</f>
-        <v>353185.83199507679</v>
+        <v>431961.0319950768</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4448,7 +4461,7 @@
         <f>K8*E14%</f>
         <v>-16473.314215610008</v>
       </c>
-      <c r="L14" s="235">
+      <c r="L14" s="220">
         <f t="shared" si="3"/>
         <v>35570.412848389999</v>
       </c>
@@ -4462,7 +4475,7 @@
       </c>
       <c r="O14" s="96">
         <f>N14+'prorrateo '!M7</f>
-        <v>225174.34265736002</v>
+        <v>302437.54265736003</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4504,7 +4517,7 @@
         <f>K8*E15%</f>
         <v>-16408.839404590006</v>
       </c>
-      <c r="L15" s="235">
+      <c r="L15" s="220">
         <f t="shared" si="3"/>
         <v>35431.194011409993</v>
       </c>
@@ -4518,7 +4531,7 @@
       </c>
       <c r="O15" s="96">
         <f>N15+'prorrateo '!M8</f>
-        <v>225196.07300211996</v>
+        <v>302156.87300211994</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4559,7 +4572,7 @@
         <f>K8*E16%</f>
         <v>-16473.314215610008</v>
       </c>
-      <c r="L16" s="235">
+      <c r="L16" s="220">
         <f t="shared" si="3"/>
         <v>35570.412848389999</v>
       </c>
@@ -4573,7 +4586,7 @@
       </c>
       <c r="O16" s="96">
         <f>N16+'prorrateo '!M9</f>
-        <v>198651.38317147997</v>
+        <v>275914.58317147999</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4614,7 +4627,7 @@
         <f>K8*E17%</f>
         <v>-16408.839404590006</v>
       </c>
-      <c r="L17" s="237">
+      <c r="L17" s="222">
         <f t="shared" si="3"/>
         <v>35431.194011409993</v>
       </c>
@@ -4628,7 +4641,7 @@
       </c>
       <c r="O17" s="96">
         <f>N17+'prorrateo '!M10</f>
-        <v>186143.16620212002</v>
+        <v>263103.96620212001</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4669,7 +4682,7 @@
         <f>K8*E18%</f>
         <v>-16247.652377040005</v>
       </c>
-      <c r="L18" s="235">
+      <c r="L18" s="220">
         <f t="shared" si="3"/>
         <v>35083.146918959996</v>
       </c>
@@ -4683,7 +4696,7 @@
       </c>
       <c r="O18" s="96">
         <f>N18+'prorrateo '!M11</f>
-        <v>349643.10529624321</v>
+        <v>425847.90529624315</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4724,7 +4737,7 @@
         <f>K8*E19%</f>
         <v>-16795.688270710005</v>
       </c>
-      <c r="L19" s="235">
+      <c r="L19" s="220">
         <f t="shared" si="3"/>
         <v>36266.507033289992</v>
       </c>
@@ -4738,7 +4751,7 @@
       </c>
       <c r="O19" s="96">
         <f>N19+'prorrateo '!M12</f>
-        <v>236901.63501827995</v>
+        <v>315676.83501827996</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4779,7 +4792,7 @@
         <f>K8*E20%</f>
         <v>-16473.314215610008</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="220">
         <f t="shared" si="3"/>
         <v>35570.412848389999</v>
       </c>
@@ -4793,7 +4806,7 @@
       </c>
       <c r="O20" s="96">
         <f>N20+'prorrateo '!M13</f>
-        <v>242506.17845736005</v>
+        <v>319769.37845736003</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4834,7 +4847,7 @@
         <f>K8*E21%</f>
         <v>-16408.839404590006</v>
       </c>
-      <c r="L21" s="235">
+      <c r="L21" s="220">
         <f t="shared" si="3"/>
         <v>35431.194011409993</v>
       </c>
@@ -4848,7 +4861,7 @@
       </c>
       <c r="O21" s="96">
         <f>N21+'prorrateo '!M14</f>
-        <v>193121.00050499284</v>
+        <v>270081.80050499283</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4889,7 +4902,7 @@
         <f>K8*E22%</f>
         <v>-16247.652377040005</v>
       </c>
-      <c r="L22" s="235">
+      <c r="L22" s="220">
         <f t="shared" si="3"/>
         <v>35083.146918959996</v>
       </c>
@@ -4903,7 +4916,7 @@
       </c>
       <c r="O22" s="96">
         <f>N22+'prorrateo '!M15</f>
-        <v>197480.06502164999</v>
+        <v>273684.86502164998</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4944,7 +4957,7 @@
         <f>K8*E23%</f>
         <v>-16795.688270710005</v>
       </c>
-      <c r="L23" s="235">
+      <c r="L23" s="220">
         <f t="shared" si="3"/>
         <v>36266.507033289992</v>
       </c>
@@ -4958,7 +4971,7 @@
       </c>
       <c r="O23" s="96">
         <f>N23+'prorrateo '!M16</f>
-        <v>245042.34046936</v>
+        <v>323817.54046936001</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4999,7 +5012,7 @@
         <f>K8*E24%</f>
         <v>-16247.652377040005</v>
       </c>
-      <c r="L24" s="235">
+      <c r="L24" s="220">
         <f t="shared" si="3"/>
         <v>35083.146918959996</v>
       </c>
@@ -5013,7 +5026,7 @@
       </c>
       <c r="O24" s="96">
         <f>N24+'prorrateo '!M17</f>
-        <v>69378.366678720005</v>
+        <v>145583.16667872001</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -5054,7 +5067,7 @@
         <f>K8*E25%</f>
         <v>-16795.688270710005</v>
       </c>
-      <c r="L25" s="235">
+      <c r="L25" s="220">
         <f t="shared" si="3"/>
         <v>36266.507033289992</v>
       </c>
@@ -5068,7 +5081,7 @@
       </c>
       <c r="O25" s="96">
         <f>N25+'prorrateo '!M18</f>
-        <v>208615.47581828001</v>
+        <v>287390.67581828003</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -5109,7 +5122,7 @@
         <f>K8*E26%</f>
         <v>-23855.680077400011</v>
       </c>
-      <c r="L26" s="235">
+      <c r="L26" s="220">
         <f t="shared" si="3"/>
         <v>51510.969682599993</v>
       </c>
@@ -5123,7 +5136,7 @@
       </c>
       <c r="O26" s="96">
         <f>N26+'prorrateo '!M19</f>
-        <v>364970.95106320007</v>
+        <v>476858.95106320013</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5152,7 +5165,7 @@
       </c>
       <c r="J27" s="185"/>
       <c r="K27" s="185"/>
-      <c r="L27" s="237">
+      <c r="L27" s="222">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5165,7 +5178,7 @@
       </c>
       <c r="O27" s="96">
         <f>N27+'prorrateo '!M20</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -5191,7 +5204,7 @@
       </c>
       <c r="J28" s="165"/>
       <c r="K28" s="114"/>
-      <c r="L28" s="235">
+      <c r="L28" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5204,7 +5217,7 @@
       </c>
       <c r="O28" s="96">
         <f>N28+'prorrateo '!M21</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -5222,8 +5235,8 @@
       <c r="H29" s="144"/>
       <c r="I29" s="154"/>
       <c r="J29" s="155"/>
-      <c r="K29" s="238"/>
-      <c r="L29" s="239">
+      <c r="K29" s="223"/>
+      <c r="L29" s="224">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5236,7 +5249,7 @@
       </c>
       <c r="O29" s="96">
         <f>N29+'prorrateo '!M22</f>
-        <v>390569.41908962413</v>
+        <v>406899.01908962411</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -5255,7 +5268,7 @@
       <c r="I30" s="164"/>
       <c r="J30" s="165"/>
       <c r="K30" s="114"/>
-      <c r="L30" s="235">
+      <c r="L30" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5268,7 +5281,7 @@
       </c>
       <c r="O30" s="96">
         <f>N30+'prorrateo '!M23</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -5289,7 +5302,7 @@
       <c r="I31" s="164"/>
       <c r="J31" s="165"/>
       <c r="K31" s="114"/>
-      <c r="L31" s="235">
+      <c r="L31" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5302,7 +5315,7 @@
       </c>
       <c r="O31" s="96">
         <f>N31+'prorrateo '!M24</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5323,7 +5336,7 @@
       <c r="I32" s="164"/>
       <c r="J32" s="165"/>
       <c r="K32" s="114"/>
-      <c r="L32" s="235">
+      <c r="L32" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5336,7 +5349,7 @@
       </c>
       <c r="O32" s="96">
         <f>N32+'prorrateo '!M25</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5357,7 +5370,7 @@
       <c r="I33" s="109"/>
       <c r="J33" s="128"/>
       <c r="K33" s="115"/>
-      <c r="L33" s="235">
+      <c r="L33" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5370,7 +5383,7 @@
       </c>
       <c r="O33" s="96">
         <f>N33+'prorrateo '!M26</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5391,7 +5404,7 @@
       <c r="I34" s="109"/>
       <c r="J34" s="128"/>
       <c r="K34" s="115"/>
-      <c r="L34" s="235">
+      <c r="L34" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5404,7 +5417,7 @@
       </c>
       <c r="O34" s="96">
         <f>N34+'prorrateo '!M27</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5430,7 +5443,7 @@
       </c>
       <c r="J35" s="166"/>
       <c r="K35" s="114"/>
-      <c r="L35" s="235">
+      <c r="L35" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5443,7 +5456,7 @@
       </c>
       <c r="O35" s="96">
         <f>N35+'prorrateo '!M28</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5471,7 +5484,7 @@
       </c>
       <c r="J36" s="166"/>
       <c r="K36" s="114"/>
-      <c r="L36" s="235">
+      <c r="L36" s="220">
         <f t="shared" si="3"/>
         <v>7517.8171969199993</v>
       </c>
@@ -5484,7 +5497,7 @@
       </c>
       <c r="O36" s="96">
         <f>N36+'prorrateo '!M29</f>
-        <v>38329.867945439997</v>
+        <v>54659.467945440003</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5505,8 +5518,8 @@
         <v>0</v>
       </c>
       <c r="J37" s="129"/>
-      <c r="K37" s="233"/>
-      <c r="L37" s="234">
+      <c r="K37" s="218"/>
+      <c r="L37" s="219">
         <v>0</v>
       </c>
       <c r="M37" s="124">
@@ -5574,18 +5587,18 @@
       <c r="A40" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="221"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
-      <c r="M40" s="219"/>
-      <c r="N40" s="219"/>
+      <c r="C40" s="236"/>
+      <c r="D40" s="234"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="234"/>
       <c r="O40" s="94"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
